--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y895"/>
+  <dimension ref="A1:Y897"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>45138</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43644</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>44455</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>44615</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45092</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44505</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>43508</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>43628</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>43970</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44186</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>44613</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>44750</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44866</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44916</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44997</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45184</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45212</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>43573</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>43766</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>44071</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44249</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44417</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>44446</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>44446</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44508</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>44740</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44750</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44750</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>44881</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44889</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45062</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45197</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45229</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45236</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>43314</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43321</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>43336</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>43339</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>43339</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>43339</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>43339</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>43340</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>43348</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>43353</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43353</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43353</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43357</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43357</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43364</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43364</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43376</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>43377</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>43381</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>43383</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>43409</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>43418</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>43420</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>43425</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>43425</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>43427</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>43427</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>43439</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>43446</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>43446</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>43448</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>43452</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>43453</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>43453</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>43453</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>43455</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>43467</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>43468</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>43470</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>43472</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>43474</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>43475</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43475</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43479</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>43479</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>43479</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>43481</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>43482</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>43482</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>43482</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>43486</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>43494</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43495</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>43496</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>43497</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>43497</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43517</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43523</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43534</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>43536</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>43537</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>43538</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>43539</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>43542</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>43544</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>43544</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>43544</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>43544</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>43544</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>43544</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>43550</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>43551</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>43552</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>43556</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>43558</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43560</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>43565</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>43565</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>43565</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>43567</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>43578</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>43579</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>43579</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>43587</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43592</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43593</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43599</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43601</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>43613</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>43613</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>43614</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>43618</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>43618</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>43619</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>43627</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>43633</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43633</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>43635</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>43646</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>43647</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>43648</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>43655</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>43658</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>43670</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>43676</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>43683</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>43690</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>43691</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>43693</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>43693</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>43694</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>43694</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>43696</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>43697</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>43698</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>43698</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>43698</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>43698</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>43700</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>43699</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>43705</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>43707</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>43707</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>43707</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>43709</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>43710</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>43711</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>43712</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>43724</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>43725</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>43731</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>43735</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>43738</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43739</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>43742</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43766</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>43766</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>43766</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>43767</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>43769</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>43769</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>43770</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43774</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43775</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>43777</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>43783</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>43783</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>43784</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43794</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43797</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43797</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>43797</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>43801</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>43803</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>43803</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>43803</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>43805</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>43809</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>43809</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>43811</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>43812</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>43815</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>43815</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>43815</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>43817</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>43817</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>43818</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>43819</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>43837</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>43838</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>43839</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>43846</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>43847</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>43850</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>43854</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>43854</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>43858</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>43859</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>43864</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>43864</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>43864</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43864</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43865</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>43868</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>43868</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>43872</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>43873</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>43873</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43874</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43874</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43880</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>43882</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>43885</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>43892</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>43892</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>43892</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>43899</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>43899</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>43899</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>43899</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>43900</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>43900</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>43900</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>43901</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>43902</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>43903</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>43907</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>43908</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>43909</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>43910</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>43913</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>43913</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>43913</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>43914</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>43915</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>43921</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>43921</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>43924</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>43927</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>43928</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>43930</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>43936</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>43938</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>43938</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>43941</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>43944</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>43944</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>43949</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>43949</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>43949</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>43959</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>43970</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>43999</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>43999</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>43999</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44004</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>44004</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44006</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44007</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>44007</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>44012</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>44015</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>44018</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44031</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>44034</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>44040</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>44041</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>44053</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>44053</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44054</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44055</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>44055</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>44056</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>44062</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44069</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44071</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>44074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>44076</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>44076</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>44076</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>44077</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44084</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>44092</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>44096</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>44099</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44099</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>44105</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44112</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44112</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>44119</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44132</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44132</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44134</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44134</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44144</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44147</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44147</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>44147</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>44152</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>44152</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>44154</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>44155</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>44161</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>44165</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44165</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>44171</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>44172</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>44173</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>44174</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>44176</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44179</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44180</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44183</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44207</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44207</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44209</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44209</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44224</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>44228</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44237</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44242</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44245</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44245</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44245</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44247</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44249</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44249</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44251</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>44252</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>44258</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>44258</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>44258</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>44258</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44264</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>44274</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>44274</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>44277</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>44293</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>44298</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>44300</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44302</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44302</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>44305</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>44305</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>44306</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>44306</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44307</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>44307</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>44309</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>44312</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44321</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44321</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44326</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44333</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44334</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44340</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>44340</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>44340</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>44340</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44341</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44341</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>44343</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>44343</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>44343</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>44348</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44349</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>44349</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>44350</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>44351</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>44356</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>44356</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44357</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44357</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>44357</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>44357</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44363</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>44365</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44367</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>44368</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>44368</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44368</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44369</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>44369</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>44370</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>44371</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>44375</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>44377</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>44377</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44379</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>44382</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44383</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44385</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44385</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>44393</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>44403</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>44412</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27161,7 +27161,7 @@
         <v>44412</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>44412</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>44417</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>44417</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>44417</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>44419</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>44421</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>44428</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44428</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44432</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44433</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44437</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44440</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44441</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>44441</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44441</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44442</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44446</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>44453</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>44453</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44460</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44466</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>44469</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44472</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44475</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44476</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44476</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44476</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44476</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44477</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44480</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44487</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44487</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44487</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44488</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44488</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44488</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44488</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44494</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44495</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44496</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44497</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44497</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44501</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44501</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44504</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44505</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44508</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44508</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44508</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44512</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44513</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44516</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44516</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44518</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44524</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44525</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44525</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44526</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44540</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44544</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44544</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44550</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44552</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44552</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44552</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44558</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44564</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44566</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44571</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44571</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>44572</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>44572</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>44572</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>44572</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>44573</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>44573</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44573</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44573</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>44578</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44578</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44581</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44585</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44585</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44592</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44593</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44594</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44595</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>44596</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>44596</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>44599</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>44599</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>44601</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>44603</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>44608</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>44613</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>44613</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>44613</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>44615</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>44615</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>44616</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33067,7 +33067,7 @@
         <v>44617</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44620</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44621</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44627</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44628</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44629</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44630</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44631</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44634</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44634</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44634</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44637</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44641</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44642</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>44648</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44648</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44648</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44648</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>44649</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>44649</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44649</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44655</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44672</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>44676</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44683</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44685</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44687</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44691</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44692</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>44692</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44692</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44692</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44692</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44698</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>44698</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>44702</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44704</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44704</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>44706</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44706</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44713</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44714</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44714</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44725</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44728</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44742</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44743</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>44749</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44750</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44750</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44750</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44750</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44755</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>44768</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44769</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44776</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44776</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>44776</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44776</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44781</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44788</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>44790</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>44790</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44798</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>44802</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>44806</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44806</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44806</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44810</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44812</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44821</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44826</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44827</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44827</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44827</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44830</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44830</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44831</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44831</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44831</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44832</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44834</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>44834</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>44835</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44838</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>44840</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>44844</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>44851</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>44851</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>44852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>44855</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44858</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44861</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44861</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>44861</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>44866</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>44866</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>44866</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44867</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>44868</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44869</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44874</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44874</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44875</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44876</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44876</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44876</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>44887</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44887</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44888</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>44889</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>44889</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>44889</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>44893</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44894</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44895</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44903</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44904</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>44907</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>44907</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44911</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44911</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44911</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44914</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44916</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>44917</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>44918</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>44928</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>44929</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44929</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44930</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44935</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44935</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44935</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44943</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44943</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44943</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44943</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44944</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44944</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44946</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44951</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44951</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>44951</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44951</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>44953</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>44956</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>44956</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44958</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>44958</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44958</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>44958</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>44965</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>44966</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>44966</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>44966</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>44971</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>44977</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>44978</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>44979</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>44980</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>44981</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>44984</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>44988</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>44993</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44997</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44997</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>44998</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45006</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45007</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45008</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45014</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45015</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45021</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45021</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45021</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45022</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45029</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45030</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45034</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45035</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45040</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45040</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45042</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>45043</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45047</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45049</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45049</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45049</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45050</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45050</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45496,7 +45496,7 @@
         <v>45054</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45553,7 +45553,7 @@
         <v>45054</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>45055</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45060</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45062</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45071</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45071</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45072</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45075</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45075</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45076</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45079</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45079</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45082</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45089</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45090</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45090</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45090</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45091</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>45091</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45091</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45092</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45096</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47092,7 +47092,7 @@
         <v>45097</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47149,7 +47149,7 @@
         <v>45097</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45098</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>45098</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45098</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>45103</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>45104</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45107</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45113</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45114</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>45121</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45124</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>45132</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>45139</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45140</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>45140</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48294,7 +48294,7 @@
         <v>45151</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48351,7 +48351,7 @@
         <v>45151</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>45151</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48465,7 +48465,7 @@
         <v>45151</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>45154</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>45155</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45155</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45162</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45162</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>45167</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45167</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>45167</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45168</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45176</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45176</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45180</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>45180</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>45180</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45181</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>45181</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45182</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45189</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>45195</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49890,7 +49890,7 @@
         <v>45195</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>45196</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>45197</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>45198</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50118,7 +50118,7 @@
         <v>45198</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50175,7 +50175,7 @@
         <v>45198</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50232,7 +50232,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>45201</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50346,7 +50346,7 @@
         <v>45202</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>45202</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45203</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45208</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>45209</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50636,7 +50636,7 @@
         <v>45210</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>45210</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>45210</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45212</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45215</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45217</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45218</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>45218</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51325,7 +51325,7 @@
         <v>45224</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>45226</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51432,14 +51432,14 @@
     <row r="869" ht="15" customHeight="1">
       <c r="A869" t="inlineStr">
         <is>
-          <t>A 53671-2023</t>
+          <t>A 53531-2023</t>
         </is>
       </c>
       <c r="B869" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         </is>
       </c>
       <c r="G869" t="n">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -51489,14 +51489,14 @@
     <row r="870" ht="15" customHeight="1">
       <c r="A870" t="inlineStr">
         <is>
-          <t>A 53531-2023</t>
+          <t>A 53677-2023</t>
         </is>
       </c>
       <c r="B870" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         </is>
       </c>
       <c r="G870" t="n">
-        <v>0.3</v>
+        <v>5</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -51546,14 +51546,14 @@
     <row r="871" ht="15" customHeight="1">
       <c r="A871" t="inlineStr">
         <is>
-          <t>A 53677-2023</t>
+          <t>A 53683-2023</t>
         </is>
       </c>
       <c r="B871" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -51603,14 +51603,14 @@
     <row r="872" ht="15" customHeight="1">
       <c r="A872" t="inlineStr">
         <is>
-          <t>A 53683-2023</t>
+          <t>A 53671-2023</t>
         </is>
       </c>
       <c r="B872" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         </is>
       </c>
       <c r="G872" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H872" t="n">
         <v>0</v>
@@ -51667,7 +51667,7 @@
         <v>45232</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>45232</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>45233</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51831,14 +51831,14 @@
     <row r="876" ht="15" customHeight="1">
       <c r="A876" t="inlineStr">
         <is>
-          <t>A 54560-2023</t>
+          <t>A 54589-2023</t>
         </is>
       </c>
       <c r="B876" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51851,7 +51851,7 @@
         </is>
       </c>
       <c r="G876" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -51888,14 +51888,14 @@
     <row r="877" ht="15" customHeight="1">
       <c r="A877" t="inlineStr">
         <is>
-          <t>A 54589-2023</t>
+          <t>A 54560-2023</t>
         </is>
       </c>
       <c r="B877" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51908,7 +51908,7 @@
         </is>
       </c>
       <c r="G877" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -51952,7 +51952,7 @@
         <v>45239</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>45239</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52059,14 +52059,14 @@
     <row r="880" ht="15" customHeight="1">
       <c r="A880" t="inlineStr">
         <is>
-          <t>A 56385-2023</t>
+          <t>A 56381-2023</t>
         </is>
       </c>
       <c r="B880" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52079,7 +52079,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>6.3</v>
+        <v>0.4</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -52116,14 +52116,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 56396-2023</t>
+          <t>A 56523-2023</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52136,7 +52136,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>9</v>
+        <v>1.9</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -52173,14 +52173,14 @@
     <row r="882" ht="15" customHeight="1">
       <c r="A882" t="inlineStr">
         <is>
-          <t>A 56381-2023</t>
+          <t>A 56527-2023</t>
         </is>
       </c>
       <c r="B882" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -52237,7 +52237,7 @@
         <v>45243</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52294,7 +52294,7 @@
         <v>45243</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52344,14 +52344,14 @@
     <row r="885" ht="15" customHeight="1">
       <c r="A885" t="inlineStr">
         <is>
-          <t>A 56523-2023</t>
+          <t>A 56385-2023</t>
         </is>
       </c>
       <c r="B885" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         </is>
       </c>
       <c r="G885" t="n">
-        <v>1.9</v>
+        <v>6.3</v>
       </c>
       <c r="H885" t="n">
         <v>0</v>
@@ -52401,14 +52401,14 @@
     <row r="886" ht="15" customHeight="1">
       <c r="A886" t="inlineStr">
         <is>
-          <t>A 56527-2023</t>
+          <t>A 56396-2023</t>
         </is>
       </c>
       <c r="B886" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         </is>
       </c>
       <c r="G886" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="H886" t="n">
         <v>0</v>
@@ -52465,7 +52465,7 @@
         <v>45244</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45244</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45250</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>45250</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>45251</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45253</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45257</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45257</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52921,62 +52921,176 @@
       </c>
       <c r="R894" s="2" t="inlineStr"/>
     </row>
-    <row r="895">
+    <row r="895" ht="15" customHeight="1">
       <c r="A895" t="inlineStr">
         <is>
-          <t>A 60023-2023</t>
+          <t>A 60066-2023</t>
         </is>
       </c>
       <c r="B895" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C895" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>BENGTSFORS</t>
+        </is>
+      </c>
+      <c r="G895" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H895" t="n">
+        <v>0</v>
+      </c>
+      <c r="I895" t="n">
+        <v>0</v>
+      </c>
+      <c r="J895" t="n">
+        <v>0</v>
+      </c>
+      <c r="K895" t="n">
+        <v>0</v>
+      </c>
+      <c r="L895" t="n">
+        <v>0</v>
+      </c>
+      <c r="M895" t="n">
+        <v>0</v>
+      </c>
+      <c r="N895" t="n">
+        <v>0</v>
+      </c>
+      <c r="O895" t="n">
+        <v>0</v>
+      </c>
+      <c r="P895" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q895" t="n">
+        <v>0</v>
+      </c>
+      <c r="R895" s="2" t="inlineStr"/>
+    </row>
+    <row r="896" ht="15" customHeight="1">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>A 60177-2023</t>
+        </is>
+      </c>
+      <c r="B896" s="1" t="n">
         <v>45258</v>
       </c>
-      <c r="D895" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E895" t="inlineStr">
-        <is>
-          <t>BENGTSFORS</t>
-        </is>
-      </c>
-      <c r="G895" t="n">
+      <c r="C896" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>BENGTSFORS</t>
+        </is>
+      </c>
+      <c r="G896" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H896" t="n">
+        <v>0</v>
+      </c>
+      <c r="I896" t="n">
+        <v>0</v>
+      </c>
+      <c r="J896" t="n">
+        <v>0</v>
+      </c>
+      <c r="K896" t="n">
+        <v>0</v>
+      </c>
+      <c r="L896" t="n">
+        <v>0</v>
+      </c>
+      <c r="M896" t="n">
+        <v>0</v>
+      </c>
+      <c r="N896" t="n">
+        <v>0</v>
+      </c>
+      <c r="O896" t="n">
+        <v>0</v>
+      </c>
+      <c r="P896" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q896" t="n">
+        <v>0</v>
+      </c>
+      <c r="R896" s="2" t="inlineStr"/>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>A 60023-2023</t>
+        </is>
+      </c>
+      <c r="B897" s="1" t="n">
+        <v>45258</v>
+      </c>
+      <c r="C897" s="1" t="n">
+        <v>45259</v>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>BENGTSFORS</t>
+        </is>
+      </c>
+      <c r="G897" t="n">
         <v>0.7</v>
       </c>
-      <c r="H895" t="n">
-        <v>0</v>
-      </c>
-      <c r="I895" t="n">
-        <v>0</v>
-      </c>
-      <c r="J895" t="n">
-        <v>0</v>
-      </c>
-      <c r="K895" t="n">
-        <v>0</v>
-      </c>
-      <c r="L895" t="n">
-        <v>0</v>
-      </c>
-      <c r="M895" t="n">
-        <v>0</v>
-      </c>
-      <c r="N895" t="n">
-        <v>0</v>
-      </c>
-      <c r="O895" t="n">
-        <v>0</v>
-      </c>
-      <c r="P895" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q895" t="n">
-        <v>0</v>
-      </c>
-      <c r="R895" s="2" t="inlineStr"/>
+      <c r="H897" t="n">
+        <v>0</v>
+      </c>
+      <c r="I897" t="n">
+        <v>0</v>
+      </c>
+      <c r="J897" t="n">
+        <v>0</v>
+      </c>
+      <c r="K897" t="n">
+        <v>0</v>
+      </c>
+      <c r="L897" t="n">
+        <v>0</v>
+      </c>
+      <c r="M897" t="n">
+        <v>0</v>
+      </c>
+      <c r="N897" t="n">
+        <v>0</v>
+      </c>
+      <c r="O897" t="n">
+        <v>0</v>
+      </c>
+      <c r="P897" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q897" t="n">
+        <v>0</v>
+      </c>
+      <c r="R897" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -564,7 +564,7 @@
         <v>45138</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43644</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>44455</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>44615</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45092</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44505</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>43508</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>43628</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>43970</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44186</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>44613</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>44750</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44866</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44916</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44997</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45184</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45212</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>43573</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>43766</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>44071</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44249</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44417</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>44446</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>44446</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44508</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>44740</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44750</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44750</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>44881</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44889</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45062</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45197</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45229</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45236</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>43314</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43321</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>43336</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>43339</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>43339</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>43339</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>43339</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>43340</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>43348</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>43353</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43353</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43353</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43357</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43357</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43364</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43364</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43376</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>43377</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>43381</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>43383</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>43409</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>43418</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>43420</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>43425</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>43425</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>43427</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>43427</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>43439</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>43446</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>43446</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>43448</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>43452</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>43453</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>43453</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>43453</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>43455</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>43467</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>43468</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>43470</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>43472</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>43474</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>43475</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43475</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43479</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>43479</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>43479</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>43481</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>43482</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>43482</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>43482</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>43486</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>43494</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43495</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>43496</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>43497</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>43497</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43517</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43523</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43534</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>43536</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>43537</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>43538</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>43539</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>43542</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>43544</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>43544</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>43544</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>43544</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>43544</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>43544</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>43550</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>43551</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>43552</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>43556</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>43558</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43560</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>43565</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>43565</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>43565</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>43567</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>43578</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>43579</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>43579</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>43587</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43592</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43593</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43599</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43601</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>43613</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>43613</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>43614</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>43618</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>43618</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>43619</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>43627</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>43633</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43633</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>43635</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>43646</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>43647</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>43648</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>43655</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>43658</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>43670</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>43676</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>43683</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>43690</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>43691</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>43693</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>43693</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>43694</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>43694</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>43696</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>43697</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>43698</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>43698</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>43698</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>43698</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>43700</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>43699</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>43705</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>43707</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>43707</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>43707</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>43709</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>43710</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>43711</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>43712</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>43724</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>43725</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>43731</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>43735</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>43738</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43739</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>43742</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43766</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>43766</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>43766</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>43767</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>43769</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>43769</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>43770</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43774</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43775</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>43777</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>43783</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>43783</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>43784</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43794</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43797</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43797</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>43797</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>43801</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>43803</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>43803</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>43803</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>43805</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>43809</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>43809</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>43811</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>43812</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>43815</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>43815</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>43815</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>43817</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>43817</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>43818</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>43819</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>43837</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>43838</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>43839</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>43846</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>43847</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>43850</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>43854</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>43854</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>43858</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>43859</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>43864</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>43864</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>43864</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43864</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43865</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>43868</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>43868</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>43872</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>43873</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>43873</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43874</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43874</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43880</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>43882</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>43885</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>43892</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>43892</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>43892</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>43899</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>43899</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>43899</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>43899</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>43900</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>43900</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>43900</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>43901</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>43902</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>43903</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>43907</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>43908</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>43909</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>43910</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>43913</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>43913</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>43913</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>43914</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>43915</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>43921</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>43921</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>43924</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>43927</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>43928</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>43930</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>43936</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>43938</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>43938</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>43941</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>43944</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>43944</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>43949</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>43949</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>43949</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>43959</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>43970</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>43999</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>43999</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>43999</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44004</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>44004</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44006</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44007</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>44007</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>44012</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>44015</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>44018</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44031</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>44034</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>44040</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>44041</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>44053</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>44053</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44054</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44055</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>44055</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>44056</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>44062</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44069</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44071</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>44074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>44076</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>44076</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>44076</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>44077</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44084</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>44092</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>44096</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>44099</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44099</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>44105</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44112</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44112</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>44119</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44132</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44132</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44134</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44134</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44144</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44147</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44147</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>44147</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>44152</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>44152</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>44154</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>44155</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>44161</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>44165</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44165</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>44171</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>44172</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>44173</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>44174</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>44176</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44179</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44180</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44183</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44207</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44207</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44209</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44209</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44224</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>44228</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44237</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44242</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44245</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44245</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44245</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44247</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44249</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44249</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44251</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>44252</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>44258</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>44258</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>44258</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>44258</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44264</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>44274</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>44274</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>44277</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>44293</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>44298</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>44300</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44302</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44302</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>44305</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>44305</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>44306</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>44306</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44307</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>44307</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>44309</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>44312</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44321</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44321</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44326</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44333</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44334</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44340</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>44340</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>44340</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>44340</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44341</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44341</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>44343</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>44343</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>44343</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>44348</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44349</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>44349</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>44350</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>44351</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>44356</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>44356</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44357</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44357</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>44357</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>44357</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44363</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>44365</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44367</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>44368</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>44368</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44368</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44369</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>44369</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>44370</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>44371</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>44375</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>44377</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>44377</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44379</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>44382</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44383</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44385</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44385</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>44393</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>44403</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>44412</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27161,7 +27161,7 @@
         <v>44412</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>44412</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>44417</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>44417</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>44417</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>44419</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>44421</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>44428</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44428</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44432</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44433</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44437</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44440</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44441</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>44441</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44441</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44442</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44446</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>44453</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>44453</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44460</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44466</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>44469</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44472</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44475</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44476</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44476</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44476</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44476</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44477</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44480</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44487</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44487</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44487</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44488</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44488</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44488</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44488</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44494</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44495</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44496</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44497</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44497</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44501</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44501</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44504</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44505</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44508</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44508</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44508</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44512</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44513</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44516</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44516</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44518</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44524</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44525</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44525</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44526</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44540</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44544</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44544</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44550</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44552</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44552</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44552</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44558</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44564</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44566</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44571</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44571</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>44572</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>44572</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>44572</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>44572</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>44573</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>44573</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44573</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44573</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>44578</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44578</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44581</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44585</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44585</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44592</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44593</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44594</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44595</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>44596</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>44596</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>44599</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>44599</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>44601</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>44603</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>44608</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>44613</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>44613</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>44613</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>44615</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>44615</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>44616</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33067,7 +33067,7 @@
         <v>44617</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44620</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44621</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44627</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44628</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44629</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44630</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44631</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44634</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44634</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44634</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44637</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44641</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44642</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>44648</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44648</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44648</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44648</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>44649</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>44649</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44649</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44655</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44672</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>44676</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44683</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44685</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44687</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44691</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44692</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>44692</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44692</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44692</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44692</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44698</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>44698</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>44702</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44704</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44704</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>44706</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44706</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44713</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44714</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44714</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44725</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44728</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44742</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44743</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>44749</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44750</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44750</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44750</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44750</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44755</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>44768</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44769</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44776</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44776</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>44776</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44776</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44781</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44788</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>44790</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>44790</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44798</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>44802</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>44806</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44806</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44806</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44810</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44812</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44821</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44826</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44827</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44827</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44827</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44830</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44830</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44831</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44831</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44831</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44832</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44834</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>44834</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>44835</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44838</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>44840</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>44844</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>44851</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>44851</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>44852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>44855</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44858</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44861</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44861</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>44861</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>44866</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>44866</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>44866</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44867</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>44868</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44869</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44874</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44874</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44875</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44876</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44876</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44876</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>44887</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44887</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44888</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>44889</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>44889</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>44889</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>44893</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44894</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44895</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44903</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44904</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>44907</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>44907</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44911</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44911</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44911</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44914</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44916</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>44917</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>44918</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>44928</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>44929</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44929</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44930</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44935</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44935</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44935</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44943</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44943</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44943</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44943</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44944</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44944</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44946</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44951</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44951</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>44951</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44951</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>44953</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>44956</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>44956</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44958</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>44958</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44958</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>44958</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>44965</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>44966</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>44966</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>44966</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>44971</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>44977</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>44978</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>44979</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>44980</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>44981</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>44984</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>44988</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>44993</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44997</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44997</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>44998</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45006</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45007</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45008</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45014</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45015</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45021</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45021</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45021</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45022</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45029</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45030</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45034</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45035</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45040</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45040</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45042</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>45043</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45047</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45049</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45049</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45049</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45050</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45050</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45496,7 +45496,7 @@
         <v>45054</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45553,7 +45553,7 @@
         <v>45054</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>45055</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45060</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45062</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45071</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45071</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45072</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45075</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45075</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45076</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45079</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45079</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45082</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45089</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45090</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45090</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45090</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45091</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>45091</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45091</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45092</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45096</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47092,7 +47092,7 @@
         <v>45097</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47149,7 +47149,7 @@
         <v>45097</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45098</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>45098</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45098</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>45103</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>45104</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45107</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45113</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45114</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>45121</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45124</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>45132</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>45139</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45140</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>45140</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48294,7 +48294,7 @@
         <v>45151</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48351,7 +48351,7 @@
         <v>45151</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>45151</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48465,7 +48465,7 @@
         <v>45151</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>45154</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>45155</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45155</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45162</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45162</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>45167</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45167</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>45167</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45168</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45176</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45176</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45180</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>45180</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>45180</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45181</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>45181</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45182</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45189</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>45195</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49890,7 +49890,7 @@
         <v>45195</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>45196</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>45197</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>45198</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50118,7 +50118,7 @@
         <v>45198</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50175,7 +50175,7 @@
         <v>45198</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50232,7 +50232,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>45201</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50346,7 +50346,7 @@
         <v>45202</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>45202</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45203</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45208</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>45209</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50636,7 +50636,7 @@
         <v>45210</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>45210</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>45210</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45212</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45215</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45217</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45218</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>45218</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51325,7 +51325,7 @@
         <v>45224</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>45226</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51432,14 +51432,14 @@
     <row r="869" ht="15" customHeight="1">
       <c r="A869" t="inlineStr">
         <is>
-          <t>A 53531-2023</t>
+          <t>A 53677-2023</t>
         </is>
       </c>
       <c r="B869" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         </is>
       </c>
       <c r="G869" t="n">
-        <v>0.3</v>
+        <v>5</v>
       </c>
       <c r="H869" t="n">
         <v>0</v>
@@ -51489,14 +51489,14 @@
     <row r="870" ht="15" customHeight="1">
       <c r="A870" t="inlineStr">
         <is>
-          <t>A 53677-2023</t>
+          <t>A 53683-2023</t>
         </is>
       </c>
       <c r="B870" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         </is>
       </c>
       <c r="G870" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -51546,14 +51546,14 @@
     <row r="871" ht="15" customHeight="1">
       <c r="A871" t="inlineStr">
         <is>
-          <t>A 53683-2023</t>
+          <t>A 53531-2023</t>
         </is>
       </c>
       <c r="B871" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         </is>
       </c>
       <c r="G871" t="n">
-        <v>6</v>
+        <v>0.3</v>
       </c>
       <c r="H871" t="n">
         <v>0</v>
@@ -51610,7 +51610,7 @@
         <v>45230</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>45232</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>45232</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51774,14 +51774,14 @@
     <row r="875" ht="15" customHeight="1">
       <c r="A875" t="inlineStr">
         <is>
-          <t>A 54590-2023</t>
+          <t>A 54560-2023</t>
         </is>
       </c>
       <c r="B875" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         </is>
       </c>
       <c r="G875" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -51838,7 +51838,7 @@
         <v>45233</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51888,14 +51888,14 @@
     <row r="877" ht="15" customHeight="1">
       <c r="A877" t="inlineStr">
         <is>
-          <t>A 54560-2023</t>
+          <t>A 54590-2023</t>
         </is>
       </c>
       <c r="B877" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51908,7 +51908,7 @@
         </is>
       </c>
       <c r="G877" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -51952,7 +51952,7 @@
         <v>45239</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>45239</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>45243</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52116,14 +52116,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 56523-2023</t>
+          <t>A 56385-2023</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52136,7 +52136,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>1.9</v>
+        <v>6.3</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -52173,14 +52173,14 @@
     <row r="882" ht="15" customHeight="1">
       <c r="A882" t="inlineStr">
         <is>
-          <t>A 56527-2023</t>
+          <t>A 56396-2023</t>
         </is>
       </c>
       <c r="B882" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -52237,7 +52237,7 @@
         <v>45243</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52294,7 +52294,7 @@
         <v>45243</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52344,14 +52344,14 @@
     <row r="885" ht="15" customHeight="1">
       <c r="A885" t="inlineStr">
         <is>
-          <t>A 56385-2023</t>
+          <t>A 56523-2023</t>
         </is>
       </c>
       <c r="B885" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         </is>
       </c>
       <c r="G885" t="n">
-        <v>6.3</v>
+        <v>1.9</v>
       </c>
       <c r="H885" t="n">
         <v>0</v>
@@ -52401,14 +52401,14 @@
     <row r="886" ht="15" customHeight="1">
       <c r="A886" t="inlineStr">
         <is>
-          <t>A 56396-2023</t>
+          <t>A 56527-2023</t>
         </is>
       </c>
       <c r="B886" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         </is>
       </c>
       <c r="G886" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="H886" t="n">
         <v>0</v>
@@ -52465,7 +52465,7 @@
         <v>45244</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45244</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45250</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>45250</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>45251</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45253</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52810,14 +52810,14 @@
     <row r="893" ht="15" customHeight="1">
       <c r="A893" t="inlineStr">
         <is>
-          <t>A 59979-2023</t>
+          <t>A 59980-2023</t>
         </is>
       </c>
       <c r="B893" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52867,14 +52867,14 @@
     <row r="894" ht="15" customHeight="1">
       <c r="A894" t="inlineStr">
         <is>
-          <t>A 59980-2023</t>
+          <t>A 59979-2023</t>
         </is>
       </c>
       <c r="B894" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45258</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52981,14 +52981,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 60177-2023</t>
+          <t>A 60023-2023</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -53038,14 +53038,14 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 60023-2023</t>
+          <t>A 60177-2023</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y897"/>
+  <dimension ref="A1:Y899"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>45138</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43644</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>44455</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>44615</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45092</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44505</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>43508</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>43628</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>43970</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44186</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>44613</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>44750</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44866</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44916</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44997</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45184</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45212</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>43573</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>43766</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>44071</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44249</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44417</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>44446</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>44446</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44508</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>44740</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44750</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44750</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>44881</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44889</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45062</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45197</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45229</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45236</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>43314</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43321</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>43336</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>43339</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>43339</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>43339</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>43339</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>43340</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>43348</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>43353</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43353</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43353</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43357</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43357</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43364</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43364</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43376</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>43377</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>43381</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>43383</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>43409</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>43418</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>43420</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>43425</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>43425</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>43427</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>43427</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>43439</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>43446</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>43446</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>43448</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>43452</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>43453</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>43453</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>43453</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>43455</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>43467</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>43468</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>43470</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>43472</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>43474</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>43475</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43475</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43479</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>43479</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>43479</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>43481</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>43482</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>43482</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>43482</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>43486</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>43494</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43495</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>43496</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>43497</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>43497</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43517</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43523</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43534</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>43536</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>43537</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>43538</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>43539</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>43542</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>43544</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>43544</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>43544</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>43544</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>43544</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>43544</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>43550</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>43551</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>43552</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>43556</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>43558</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43560</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>43565</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>43565</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>43565</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>43567</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>43578</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>43579</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>43579</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>43587</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43592</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43593</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43599</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43601</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>43613</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>43613</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>43614</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>43618</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>43618</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>43619</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>43627</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>43633</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43633</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>43635</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>43646</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>43647</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>43648</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>43655</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>43658</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>43670</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>43676</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>43683</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>43690</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>43691</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>43693</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>43693</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>43694</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>43694</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>43696</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>43697</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>43698</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>43698</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>43698</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>43698</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>43700</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>43699</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>43705</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>43707</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>43707</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>43707</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>43709</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>43710</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>43711</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>43712</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>43724</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>43725</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>43731</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>43735</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>43738</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43739</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>43742</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43766</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>43766</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>43766</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>43767</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>43769</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>43769</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>43770</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43774</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43775</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>43777</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>43783</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>43783</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>43784</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43794</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43797</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43797</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>43797</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>43801</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>43803</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>43803</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>43803</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>43805</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>43809</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>43809</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>43811</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>43812</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>43815</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>43815</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>43815</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>43817</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>43817</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>43818</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>43819</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>43837</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>43838</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>43839</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>43846</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>43847</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>43850</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>43854</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>43854</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>43858</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>43859</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>43864</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>43864</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>43864</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43864</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43865</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>43868</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>43868</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>43872</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>43873</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>43873</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43874</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43874</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43880</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>43882</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>43885</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>43892</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>43892</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>43892</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>43899</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>43899</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>43899</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>43899</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>43900</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>43900</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>43900</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>43901</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>43902</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>43903</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>43907</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>43908</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>43909</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>43910</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>43913</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>43913</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>43913</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>43914</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>43915</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>43921</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>43921</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>43924</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>43927</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>43928</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>43930</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>43936</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>43938</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>43938</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>43941</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>43944</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>43944</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>43949</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>43949</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>43949</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>43959</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>43970</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>43999</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>43999</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>43999</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44004</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>44004</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44006</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44007</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>44007</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>44012</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>44015</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>44018</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44031</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>44034</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>44040</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>44041</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>44053</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>44053</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44054</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44055</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>44055</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>44056</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>44062</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44069</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44071</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>44074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>44076</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>44076</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>44076</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>44077</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44084</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>44092</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>44096</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>44099</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44099</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>44105</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44112</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44112</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>44119</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44132</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44132</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44134</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44134</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44144</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44147</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44147</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>44147</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>44152</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>44152</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>44154</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>44155</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>44161</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>44165</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44165</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>44171</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>44172</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>44173</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>44174</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>44176</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44179</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44180</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44183</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44207</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44207</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44209</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44209</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44224</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>44228</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44237</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44242</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44245</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44245</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44245</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44247</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44249</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44249</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44251</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>44252</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>44258</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>44258</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>44258</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>44258</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44264</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>44274</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>44274</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>44277</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>44293</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>44298</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>44300</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44302</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44302</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>44305</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>44305</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>44306</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>44306</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44307</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>44307</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>44309</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>44312</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44321</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44321</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44326</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44333</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44334</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44340</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>44340</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>44340</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>44340</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44341</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44341</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>44343</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>44343</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>44343</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>44348</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44349</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>44349</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>44350</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>44351</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>44356</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>44356</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44357</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44357</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>44357</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>44357</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44363</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>44365</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44367</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>44368</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>44368</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44368</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44369</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>44369</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>44370</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>44371</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>44375</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>44377</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>44377</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44379</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>44382</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44383</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44385</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44385</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>44393</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>44403</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>44412</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27161,7 +27161,7 @@
         <v>44412</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>44412</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>44417</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>44417</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>44417</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>44419</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>44421</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>44428</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44428</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44432</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44433</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44437</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44440</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44441</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>44441</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44441</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44442</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44446</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>44453</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>44453</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44460</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44466</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>44469</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44472</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44475</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44476</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44476</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44476</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44476</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44477</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44480</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44487</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44487</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44487</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44488</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44488</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44488</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44488</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44494</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44495</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44496</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44497</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44497</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44501</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44501</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44504</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44505</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44508</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44508</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44508</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44512</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44513</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44516</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44516</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44518</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44524</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44525</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44525</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44526</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44540</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44544</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44544</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44550</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44552</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44552</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44552</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44558</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44564</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44566</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44571</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44571</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>44572</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>44572</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>44572</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>44572</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>44573</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>44573</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44573</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44573</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>44578</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44578</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44581</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44585</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44585</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44592</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44593</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44594</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44595</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>44596</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>44596</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>44599</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>44599</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>44601</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>44603</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>44608</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>44613</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>44613</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>44613</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>44615</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>44615</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>44616</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33067,7 +33067,7 @@
         <v>44617</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44620</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44621</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44627</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44628</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44629</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44630</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44631</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44634</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44634</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44634</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44637</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44641</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44642</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>44648</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44648</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44648</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44648</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>44649</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>44649</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44649</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44655</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44672</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>44676</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44683</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44685</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44687</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44691</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44692</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>44692</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44692</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44692</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44692</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44698</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>44698</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>44702</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44704</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44704</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>44706</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44706</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44713</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44714</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44714</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44725</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44728</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44742</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44743</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>44749</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44750</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44750</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44750</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44750</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44755</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>44768</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44769</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44776</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44776</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>44776</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44776</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44781</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44788</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>44790</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>44790</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44798</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>44802</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>44806</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44806</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44806</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44810</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44812</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44821</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44826</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44827</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44827</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44827</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44830</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44830</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44831</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44831</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44831</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44832</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44834</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>44834</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>44835</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44838</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>44840</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>44844</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>44851</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>44851</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>44852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>44855</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44858</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44861</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44861</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>44861</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>44866</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>44866</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>44866</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44867</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>44868</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44869</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44874</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44874</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44875</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44876</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44876</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44876</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>44887</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44887</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44888</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>44889</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>44889</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>44889</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>44893</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44894</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44895</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44903</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44904</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>44907</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>44907</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44911</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44911</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44911</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44914</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44916</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>44917</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>44918</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>44928</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>44929</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44929</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44930</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44935</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44935</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44935</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44943</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44943</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44943</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44943</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44944</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44944</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44946</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44951</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44951</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>44951</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44951</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>44953</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>44956</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>44956</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44958</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>44958</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44958</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>44958</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>44965</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>44966</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>44966</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>44966</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>44971</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>44977</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>44978</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>44979</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>44980</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>44981</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>44984</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>44988</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>44993</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44997</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44997</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>44998</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45006</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45007</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45008</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45014</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45015</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45021</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45021</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45021</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45022</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45029</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45030</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45034</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45035</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45040</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45040</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45042</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>45043</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45047</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45049</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45049</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45049</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45050</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45050</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45496,7 +45496,7 @@
         <v>45054</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45553,7 +45553,7 @@
         <v>45054</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>45055</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45060</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45062</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45071</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45071</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45072</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45075</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45075</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45076</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45079</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45079</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45082</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45089</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45090</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45090</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45090</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45091</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>45091</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45091</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45092</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45096</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47092,7 +47092,7 @@
         <v>45097</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47149,7 +47149,7 @@
         <v>45097</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45098</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>45098</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45098</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>45103</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>45104</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45107</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45113</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45114</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>45121</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45124</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>45132</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>45139</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45140</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>45140</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48294,7 +48294,7 @@
         <v>45151</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48351,7 +48351,7 @@
         <v>45151</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>45151</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48465,7 +48465,7 @@
         <v>45151</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>45154</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>45155</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45155</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45162</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45162</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>45167</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45167</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>45167</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45168</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45176</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45176</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45180</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>45180</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>45180</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45181</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>45181</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45182</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45189</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>45195</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49890,7 +49890,7 @@
         <v>45195</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>45196</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>45197</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>45198</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50118,7 +50118,7 @@
         <v>45198</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50175,7 +50175,7 @@
         <v>45198</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50232,7 +50232,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>45201</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50346,7 +50346,7 @@
         <v>45202</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>45202</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45203</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45208</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>45209</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50636,7 +50636,7 @@
         <v>45210</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>45210</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>45210</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45212</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45215</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45217</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45218</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>45218</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51325,7 +51325,7 @@
         <v>45224</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>45226</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>45230</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51496,7 +51496,7 @@
         <v>45230</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>45230</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>45230</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>45232</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>45232</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>45233</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>45233</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45233</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>45239</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>45239</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52059,14 +52059,14 @@
     <row r="880" ht="15" customHeight="1">
       <c r="A880" t="inlineStr">
         <is>
-          <t>A 56381-2023</t>
+          <t>A 56385-2023</t>
         </is>
       </c>
       <c r="B880" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52079,7 +52079,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>0.4</v>
+        <v>6.3</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -52116,14 +52116,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 56385-2023</t>
+          <t>A 56396-2023</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52136,7 +52136,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -52173,14 +52173,14 @@
     <row r="882" ht="15" customHeight="1">
       <c r="A882" t="inlineStr">
         <is>
-          <t>A 56396-2023</t>
+          <t>A 56381-2023</t>
         </is>
       </c>
       <c r="B882" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>9</v>
+        <v>0.4</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -52230,14 +52230,14 @@
     <row r="883" ht="15" customHeight="1">
       <c r="A883" t="inlineStr">
         <is>
-          <t>A 56580-2023</t>
+          <t>A 56523-2023</t>
         </is>
       </c>
       <c r="B883" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52250,7 +52250,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -52287,14 +52287,14 @@
     <row r="884" ht="15" customHeight="1">
       <c r="A884" t="inlineStr">
         <is>
-          <t>A 56629-2023</t>
+          <t>A 56527-2023</t>
         </is>
       </c>
       <c r="B884" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52307,7 +52307,7 @@
         </is>
       </c>
       <c r="G884" t="n">
-        <v>9.6</v>
+        <v>3.8</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -52344,14 +52344,14 @@
     <row r="885" ht="15" customHeight="1">
       <c r="A885" t="inlineStr">
         <is>
-          <t>A 56523-2023</t>
+          <t>A 56629-2023</t>
         </is>
       </c>
       <c r="B885" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         </is>
       </c>
       <c r="G885" t="n">
-        <v>1.9</v>
+        <v>9.6</v>
       </c>
       <c r="H885" t="n">
         <v>0</v>
@@ -52401,14 +52401,14 @@
     <row r="886" ht="15" customHeight="1">
       <c r="A886" t="inlineStr">
         <is>
-          <t>A 56527-2023</t>
+          <t>A 56580-2023</t>
         </is>
       </c>
       <c r="B886" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         </is>
       </c>
       <c r="G886" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="H886" t="n">
         <v>0</v>
@@ -52465,7 +52465,7 @@
         <v>45244</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45244</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45250</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>45250</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>45251</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45253</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45257</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45257</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52924,14 +52924,14 @@
     <row r="895" ht="15" customHeight="1">
       <c r="A895" t="inlineStr">
         <is>
-          <t>A 60066-2023</t>
+          <t>A 60023-2023</t>
         </is>
       </c>
       <c r="B895" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="H895" t="n">
         <v>0</v>
@@ -52981,14 +52981,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 60023-2023</t>
+          <t>A 60177-2023</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -53035,62 +53035,176 @@
       </c>
       <c r="R896" s="2" t="inlineStr"/>
     </row>
-    <row r="897">
+    <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 60177-2023</t>
+          <t>A 60066-2023</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C897" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>BENGTSFORS</t>
+        </is>
+      </c>
+      <c r="G897" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H897" t="n">
+        <v>0</v>
+      </c>
+      <c r="I897" t="n">
+        <v>0</v>
+      </c>
+      <c r="J897" t="n">
+        <v>0</v>
+      </c>
+      <c r="K897" t="n">
+        <v>0</v>
+      </c>
+      <c r="L897" t="n">
+        <v>0</v>
+      </c>
+      <c r="M897" t="n">
+        <v>0</v>
+      </c>
+      <c r="N897" t="n">
+        <v>0</v>
+      </c>
+      <c r="O897" t="n">
+        <v>0</v>
+      </c>
+      <c r="P897" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q897" t="n">
+        <v>0</v>
+      </c>
+      <c r="R897" s="2" t="inlineStr"/>
+    </row>
+    <row r="898" ht="15" customHeight="1">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>A 60739-2023</t>
+        </is>
+      </c>
+      <c r="B898" s="1" t="n">
         <v>45260</v>
       </c>
-      <c r="D897" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E897" t="inlineStr">
-        <is>
-          <t>BENGTSFORS</t>
-        </is>
-      </c>
-      <c r="G897" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H897" t="n">
-        <v>0</v>
-      </c>
-      <c r="I897" t="n">
-        <v>0</v>
-      </c>
-      <c r="J897" t="n">
-        <v>0</v>
-      </c>
-      <c r="K897" t="n">
-        <v>0</v>
-      </c>
-      <c r="L897" t="n">
-        <v>0</v>
-      </c>
-      <c r="M897" t="n">
-        <v>0</v>
-      </c>
-      <c r="N897" t="n">
-        <v>0</v>
-      </c>
-      <c r="O897" t="n">
-        <v>0</v>
-      </c>
-      <c r="P897" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q897" t="n">
-        <v>0</v>
-      </c>
-      <c r="R897" s="2" t="inlineStr"/>
+      <c r="C898" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>BENGTSFORS</t>
+        </is>
+      </c>
+      <c r="G898" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H898" t="n">
+        <v>0</v>
+      </c>
+      <c r="I898" t="n">
+        <v>0</v>
+      </c>
+      <c r="J898" t="n">
+        <v>0</v>
+      </c>
+      <c r="K898" t="n">
+        <v>0</v>
+      </c>
+      <c r="L898" t="n">
+        <v>0</v>
+      </c>
+      <c r="M898" t="n">
+        <v>0</v>
+      </c>
+      <c r="N898" t="n">
+        <v>0</v>
+      </c>
+      <c r="O898" t="n">
+        <v>0</v>
+      </c>
+      <c r="P898" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q898" t="n">
+        <v>0</v>
+      </c>
+      <c r="R898" s="2" t="inlineStr"/>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>A 60679-2023</t>
+        </is>
+      </c>
+      <c r="B899" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="C899" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>BENGTSFORS</t>
+        </is>
+      </c>
+      <c r="G899" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H899" t="n">
+        <v>0</v>
+      </c>
+      <c r="I899" t="n">
+        <v>0</v>
+      </c>
+      <c r="J899" t="n">
+        <v>0</v>
+      </c>
+      <c r="K899" t="n">
+        <v>0</v>
+      </c>
+      <c r="L899" t="n">
+        <v>0</v>
+      </c>
+      <c r="M899" t="n">
+        <v>0</v>
+      </c>
+      <c r="N899" t="n">
+        <v>0</v>
+      </c>
+      <c r="O899" t="n">
+        <v>0</v>
+      </c>
+      <c r="P899" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q899" t="n">
+        <v>0</v>
+      </c>
+      <c r="R899" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y899"/>
+  <dimension ref="A1:Y900"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>45138</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43644</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>44455</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>44615</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45092</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44505</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>43508</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>43628</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>43970</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44186</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>44613</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>44750</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44866</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44916</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44997</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45184</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45212</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>43573</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>43766</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>44071</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44249</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44417</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>44446</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>44446</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44508</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>44740</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44750</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44750</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>44881</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44889</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45062</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45197</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45229</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45236</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>43314</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43321</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>43336</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>43339</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>43339</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>43339</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>43339</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>43340</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>43348</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>43353</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43353</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43353</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43357</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43357</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43364</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43364</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43376</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>43377</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>43381</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>43383</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>43409</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>43418</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>43420</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>43425</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>43425</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>43427</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>43427</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>43439</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>43446</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>43446</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>43448</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>43452</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>43453</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>43453</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>43453</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>43455</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>43467</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>43468</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>43470</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>43472</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>43474</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>43475</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43475</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43479</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>43479</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>43479</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>43481</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>43482</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>43482</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>43482</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>43486</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>43494</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43495</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>43496</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>43497</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>43497</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43517</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43523</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43534</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>43536</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>43537</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>43538</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>43539</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>43542</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>43544</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>43544</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>43544</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>43544</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>43544</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>43544</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>43550</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>43551</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>43552</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>43556</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>43558</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43560</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>43565</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>43565</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>43565</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>43567</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>43578</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>43579</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>43579</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>43587</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43592</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43593</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43599</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43601</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>43613</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>43613</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>43614</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>43618</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>43618</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>43619</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>43627</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>43633</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43633</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>43635</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>43646</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>43647</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>43648</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>43655</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>43658</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>43670</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>43676</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>43683</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>43690</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>43691</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>43693</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>43693</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>43694</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>43694</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>43696</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>43697</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>43698</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>43698</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>43698</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>43698</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>43700</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>43699</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>43705</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>43707</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>43707</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>43707</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>43709</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>43710</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>43711</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>43712</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>43724</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>43725</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>43731</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>43735</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>43738</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43739</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>43742</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43766</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>43766</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>43766</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>43767</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>43769</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>43769</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>43770</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43774</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43775</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>43777</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>43783</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>43783</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>43784</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43794</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43797</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43797</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>43797</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>43801</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>43803</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>43803</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>43803</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>43805</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>43809</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>43809</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>43811</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>43812</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>43815</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>43815</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>43815</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>43817</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>43817</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>43818</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>43819</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>43837</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>43838</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>43839</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>43846</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>43847</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>43850</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>43854</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>43854</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>43858</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>43859</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>43864</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>43864</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>43864</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43864</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43865</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>43868</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>43868</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>43872</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>43873</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>43873</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43874</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43874</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43880</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>43882</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>43885</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>43892</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>43892</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>43892</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>43899</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>43899</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>43899</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>43899</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>43900</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>43900</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>43900</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>43901</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>43902</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>43903</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>43907</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>43908</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>43909</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>43910</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>43913</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>43913</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>43913</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>43914</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>43915</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>43921</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>43921</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>43924</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>43927</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>43928</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>43930</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>43936</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>43938</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>43938</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>43941</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>43944</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>43944</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>43949</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>43949</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>43949</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>43959</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>43970</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>43999</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>43999</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>43999</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44004</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>44004</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44006</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44007</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>44007</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>44012</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>44015</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>44018</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44031</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>44034</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>44040</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>44041</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>44053</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>44053</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44054</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44055</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>44055</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>44056</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>44062</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44069</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44071</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>44074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>44076</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>44076</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>44076</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>44077</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44084</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>44092</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>44096</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>44099</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44099</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>44105</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44112</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44112</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>44119</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44132</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44132</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44134</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44134</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44144</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44147</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44147</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>44147</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>44152</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>44152</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>44154</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>44155</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>44161</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>44165</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44165</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>44171</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>44172</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>44173</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>44174</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>44176</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44179</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44180</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44183</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44207</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44207</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44209</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44209</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44224</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>44228</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44237</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44242</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44245</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44245</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44245</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44247</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44249</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44249</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44251</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>44252</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>44258</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>44258</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>44258</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>44258</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44264</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>44274</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>44274</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>44277</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>44293</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>44298</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>44300</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44302</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44302</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>44305</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>44305</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>44306</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>44306</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44307</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>44307</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>44309</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>44312</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44321</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44321</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44326</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44333</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44334</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44340</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>44340</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>44340</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>44340</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44341</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44341</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>44343</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>44343</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>44343</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>44348</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44349</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>44349</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>44350</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>44351</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>44356</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>44356</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44357</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44357</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>44357</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>44357</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44363</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>44365</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44367</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>44368</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>44368</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44368</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44369</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>44369</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>44370</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>44371</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>44375</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>44377</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>44377</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44379</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>44382</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44383</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44385</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44385</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>44393</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>44403</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>44412</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27161,7 +27161,7 @@
         <v>44412</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>44412</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>44417</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>44417</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>44417</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>44419</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>44421</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>44428</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44428</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44432</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44433</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44437</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44440</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44441</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>44441</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44441</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44442</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44446</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>44453</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>44453</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44460</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44466</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>44469</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44472</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44475</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44476</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44476</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44476</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44476</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44477</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44480</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44487</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44487</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44487</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44488</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44488</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44488</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44488</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44494</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44495</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44496</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44497</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44497</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44501</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44501</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44504</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44505</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44508</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44508</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44508</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44512</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44513</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44516</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44516</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44518</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44524</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44525</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44525</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44526</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44540</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44544</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44544</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44550</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44552</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44552</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44552</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44558</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44564</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44566</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44571</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44571</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>44572</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>44572</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>44572</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>44572</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>44573</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>44573</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44573</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44573</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>44578</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44578</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44581</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44585</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44585</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44592</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44593</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44594</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44595</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>44596</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>44596</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>44599</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>44599</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>44601</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>44603</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>44608</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>44613</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>44613</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>44613</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>44615</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>44615</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>44616</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33067,7 +33067,7 @@
         <v>44617</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44620</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44621</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44627</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44628</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44629</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44630</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44631</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44634</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44634</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44634</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44637</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44641</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44642</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>44648</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44648</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44648</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44648</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>44649</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>44649</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44649</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44655</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44672</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>44676</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44683</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44685</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44687</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44691</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44692</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>44692</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44692</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44692</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44692</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44698</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>44698</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>44702</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44704</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44704</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>44706</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44706</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44713</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44714</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44714</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44725</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44728</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44742</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44743</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>44749</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44750</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44750</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44750</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44750</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44755</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>44768</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44769</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44776</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44776</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>44776</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44776</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44781</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44788</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>44790</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>44790</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44798</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>44802</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>44806</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44806</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44806</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44810</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44812</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44821</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44826</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44827</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44827</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44827</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44830</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44830</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44831</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44831</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44831</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44832</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44834</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>44834</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>44835</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44838</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>44840</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>44844</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>44851</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>44851</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>44852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>44855</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44858</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44861</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44861</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>44861</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>44866</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>44866</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>44866</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44867</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>44868</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44869</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44874</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44874</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44875</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44876</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44876</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44876</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>44887</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44887</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44888</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>44889</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>44889</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>44889</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>44893</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44894</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44895</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44903</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44904</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>44907</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>44907</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44911</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44911</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44911</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44914</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44916</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>44917</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>44918</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>44928</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>44929</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44929</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44930</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44935</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44935</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44935</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44943</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44943</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44943</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44943</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44944</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44944</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44946</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44951</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44951</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>44951</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44951</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>44953</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>44956</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>44956</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44958</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>44958</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44958</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>44958</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>44965</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>44966</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>44966</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>44966</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>44971</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>44977</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>44978</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>44979</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>44980</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>44981</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>44984</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>44988</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>44993</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44997</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44997</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>44998</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45006</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45007</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45008</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45014</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45015</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45021</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45021</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45021</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45022</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45029</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45030</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45034</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45035</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45040</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45040</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45042</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>45043</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45047</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45049</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45049</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45049</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45050</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45050</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45496,7 +45496,7 @@
         <v>45054</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45553,7 +45553,7 @@
         <v>45054</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>45055</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45060</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45062</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45071</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45071</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45072</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45075</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45075</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45076</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45079</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45079</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45082</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45089</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45090</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45090</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45090</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45091</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>45091</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45091</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45092</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45096</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47092,7 +47092,7 @@
         <v>45097</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47149,7 +47149,7 @@
         <v>45097</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45098</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>45098</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45098</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>45103</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>45104</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45107</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45113</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45114</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>45121</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45124</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>45132</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>45139</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45140</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>45140</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48294,7 +48294,7 @@
         <v>45151</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48351,7 +48351,7 @@
         <v>45151</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>45151</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48465,7 +48465,7 @@
         <v>45151</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>45154</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>45155</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45155</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45162</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45162</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>45167</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45167</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>45167</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45168</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45176</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45176</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45180</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>45180</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>45180</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45181</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>45181</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45182</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45189</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>45195</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49890,7 +49890,7 @@
         <v>45195</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>45196</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>45197</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>45198</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50118,7 +50118,7 @@
         <v>45198</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50175,7 +50175,7 @@
         <v>45198</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50232,7 +50232,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>45201</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50346,7 +50346,7 @@
         <v>45202</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>45202</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45203</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45208</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>45209</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50636,7 +50636,7 @@
         <v>45210</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>45210</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>45210</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45212</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45215</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45217</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45218</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>45218</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51325,7 +51325,7 @@
         <v>45224</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>45226</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>45230</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51496,7 +51496,7 @@
         <v>45230</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>45230</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>45230</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>45232</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>45232</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51774,14 +51774,14 @@
     <row r="875" ht="15" customHeight="1">
       <c r="A875" t="inlineStr">
         <is>
-          <t>A 54560-2023</t>
+          <t>A 54590-2023</t>
         </is>
       </c>
       <c r="B875" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         </is>
       </c>
       <c r="G875" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -51831,14 +51831,14 @@
     <row r="876" ht="15" customHeight="1">
       <c r="A876" t="inlineStr">
         <is>
-          <t>A 54589-2023</t>
+          <t>A 54560-2023</t>
         </is>
       </c>
       <c r="B876" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51851,7 +51851,7 @@
         </is>
       </c>
       <c r="G876" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -51888,14 +51888,14 @@
     <row r="877" ht="15" customHeight="1">
       <c r="A877" t="inlineStr">
         <is>
-          <t>A 54590-2023</t>
+          <t>A 54589-2023</t>
         </is>
       </c>
       <c r="B877" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51908,7 +51908,7 @@
         </is>
       </c>
       <c r="G877" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -51945,14 +51945,14 @@
     <row r="878" ht="15" customHeight="1">
       <c r="A878" t="inlineStr">
         <is>
-          <t>A 55700-2023</t>
+          <t>A 55819-2023</t>
         </is>
       </c>
       <c r="B878" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51965,7 +51965,7 @@
         </is>
       </c>
       <c r="G878" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -52002,14 +52002,14 @@
     <row r="879" ht="15" customHeight="1">
       <c r="A879" t="inlineStr">
         <is>
-          <t>A 55819-2023</t>
+          <t>A 55700-2023</t>
         </is>
       </c>
       <c r="B879" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52022,7 +52022,7 @@
         </is>
       </c>
       <c r="G879" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H879" t="n">
         <v>0</v>
@@ -52059,14 +52059,14 @@
     <row r="880" ht="15" customHeight="1">
       <c r="A880" t="inlineStr">
         <is>
-          <t>A 56385-2023</t>
+          <t>A 56381-2023</t>
         </is>
       </c>
       <c r="B880" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52079,7 +52079,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>6.3</v>
+        <v>0.4</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -52116,14 +52116,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 56396-2023</t>
+          <t>A 56385-2023</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52136,7 +52136,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>9</v>
+        <v>6.3</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -52173,14 +52173,14 @@
     <row r="882" ht="15" customHeight="1">
       <c r="A882" t="inlineStr">
         <is>
-          <t>A 56381-2023</t>
+          <t>A 56396-2023</t>
         </is>
       </c>
       <c r="B882" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>0.4</v>
+        <v>9</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -52237,7 +52237,7 @@
         <v>45243</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52294,7 +52294,7 @@
         <v>45243</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52344,14 +52344,14 @@
     <row r="885" ht="15" customHeight="1">
       <c r="A885" t="inlineStr">
         <is>
-          <t>A 56629-2023</t>
+          <t>A 56580-2023</t>
         </is>
       </c>
       <c r="B885" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         </is>
       </c>
       <c r="G885" t="n">
-        <v>9.6</v>
+        <v>1</v>
       </c>
       <c r="H885" t="n">
         <v>0</v>
@@ -52401,14 +52401,14 @@
     <row r="886" ht="15" customHeight="1">
       <c r="A886" t="inlineStr">
         <is>
-          <t>A 56580-2023</t>
+          <t>A 56629-2023</t>
         </is>
       </c>
       <c r="B886" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         </is>
       </c>
       <c r="G886" t="n">
-        <v>1</v>
+        <v>9.6</v>
       </c>
       <c r="H886" t="n">
         <v>0</v>
@@ -52465,7 +52465,7 @@
         <v>45244</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45244</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45250</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>45250</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>45251</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45253</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52810,14 +52810,14 @@
     <row r="893" ht="15" customHeight="1">
       <c r="A893" t="inlineStr">
         <is>
-          <t>A 59980-2023</t>
+          <t>A 59979-2023</t>
         </is>
       </c>
       <c r="B893" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52867,14 +52867,14 @@
     <row r="894" ht="15" customHeight="1">
       <c r="A894" t="inlineStr">
         <is>
-          <t>A 59979-2023</t>
+          <t>A 59980-2023</t>
         </is>
       </c>
       <c r="B894" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52924,14 +52924,14 @@
     <row r="895" ht="15" customHeight="1">
       <c r="A895" t="inlineStr">
         <is>
-          <t>A 60023-2023</t>
+          <t>A 60177-2023</t>
         </is>
       </c>
       <c r="B895" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="H895" t="n">
         <v>0</v>
@@ -52981,14 +52981,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 60177-2023</t>
+          <t>A 60023-2023</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -53045,7 +53045,7 @@
         <v>45258</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53095,14 +53095,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 60739-2023</t>
+          <t>A 60679-2023</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -53149,62 +53149,119 @@
       </c>
       <c r="R898" s="2" t="inlineStr"/>
     </row>
-    <row r="899">
+    <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 60679-2023</t>
+          <t>A 60739-2023</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C899" s="1" t="n">
+        <v>45262</v>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>BENGTSFORS</t>
+        </is>
+      </c>
+      <c r="G899" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H899" t="n">
+        <v>0</v>
+      </c>
+      <c r="I899" t="n">
+        <v>0</v>
+      </c>
+      <c r="J899" t="n">
+        <v>0</v>
+      </c>
+      <c r="K899" t="n">
+        <v>0</v>
+      </c>
+      <c r="L899" t="n">
+        <v>0</v>
+      </c>
+      <c r="M899" t="n">
+        <v>0</v>
+      </c>
+      <c r="N899" t="n">
+        <v>0</v>
+      </c>
+      <c r="O899" t="n">
+        <v>0</v>
+      </c>
+      <c r="P899" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q899" t="n">
+        <v>0</v>
+      </c>
+      <c r="R899" s="2" t="inlineStr"/>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>A 60909-2023</t>
+        </is>
+      </c>
+      <c r="B900" s="1" t="n">
         <v>45261</v>
       </c>
-      <c r="D899" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E899" t="inlineStr">
-        <is>
-          <t>BENGTSFORS</t>
-        </is>
-      </c>
-      <c r="G899" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H899" t="n">
-        <v>0</v>
-      </c>
-      <c r="I899" t="n">
-        <v>0</v>
-      </c>
-      <c r="J899" t="n">
-        <v>0</v>
-      </c>
-      <c r="K899" t="n">
-        <v>0</v>
-      </c>
-      <c r="L899" t="n">
-        <v>0</v>
-      </c>
-      <c r="M899" t="n">
-        <v>0</v>
-      </c>
-      <c r="N899" t="n">
-        <v>0</v>
-      </c>
-      <c r="O899" t="n">
-        <v>0</v>
-      </c>
-      <c r="P899" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q899" t="n">
-        <v>0</v>
-      </c>
-      <c r="R899" s="2" t="inlineStr"/>
+      <c r="C900" s="1" t="n">
+        <v>45262</v>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>BENGTSFORS</t>
+        </is>
+      </c>
+      <c r="G900" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H900" t="n">
+        <v>0</v>
+      </c>
+      <c r="I900" t="n">
+        <v>0</v>
+      </c>
+      <c r="J900" t="n">
+        <v>0</v>
+      </c>
+      <c r="K900" t="n">
+        <v>0</v>
+      </c>
+      <c r="L900" t="n">
+        <v>0</v>
+      </c>
+      <c r="M900" t="n">
+        <v>0</v>
+      </c>
+      <c r="N900" t="n">
+        <v>0</v>
+      </c>
+      <c r="O900" t="n">
+        <v>0</v>
+      </c>
+      <c r="P900" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q900" t="n">
+        <v>0</v>
+      </c>
+      <c r="R900" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -564,7 +564,7 @@
         <v>45138</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43644</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>44455</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>44615</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45092</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44505</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>43508</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>43628</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>43970</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44186</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>44613</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>44750</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44866</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44916</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44997</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45184</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45212</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>43573</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>43766</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>44071</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44249</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44417</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>44446</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>44446</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44508</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>44740</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44750</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44750</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>44881</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44889</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45062</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45197</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45229</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45236</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>43314</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43321</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>43336</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>43339</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>43339</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>43339</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>43339</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>43340</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>43348</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>43353</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43353</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43353</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43357</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43357</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43364</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43364</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43376</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>43377</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>43381</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>43383</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>43409</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>43418</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>43420</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>43425</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>43425</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>43427</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>43427</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>43439</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>43446</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>43446</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>43448</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>43452</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>43453</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>43453</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>43453</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>43455</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>43467</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>43468</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>43470</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>43472</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>43474</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>43475</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43475</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43479</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>43479</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>43479</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>43481</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>43482</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>43482</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>43482</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>43486</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>43494</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43495</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>43496</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>43497</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>43497</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43517</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43523</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43534</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>43536</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>43537</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>43538</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>43539</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>43542</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>43544</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>43544</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>43544</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>43544</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>43544</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>43544</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>43550</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>43551</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>43552</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>43556</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>43558</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43560</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>43565</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>43565</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>43565</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>43567</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>43578</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>43579</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>43579</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>43587</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43592</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43593</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43599</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43601</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>43613</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>43613</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>43614</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>43618</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>43618</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>43619</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>43627</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>43633</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43633</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>43635</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>43646</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>43647</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>43648</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>43655</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>43658</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>43670</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>43676</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>43683</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>43690</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>43691</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>43693</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>43693</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>43694</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>43694</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>43696</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>43697</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>43698</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>43698</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>43698</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>43698</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>43700</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>43699</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>43705</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>43707</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>43707</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>43707</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>43709</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>43710</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>43711</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>43712</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>43724</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>43725</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>43731</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>43735</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>43738</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43739</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>43742</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43766</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>43766</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>43766</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>43767</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>43769</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>43769</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>43770</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43774</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43775</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>43777</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>43783</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>43783</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>43784</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43794</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43797</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43797</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>43797</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>43801</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>43803</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>43803</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>43803</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>43805</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>43809</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>43809</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>43811</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>43812</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>43815</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>43815</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>43815</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>43817</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>43817</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>43818</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>43819</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>43837</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>43838</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>43839</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>43846</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>43847</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>43850</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>43854</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>43854</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>43858</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>43859</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>43864</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>43864</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>43864</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43864</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43865</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>43868</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>43868</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>43872</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>43873</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>43873</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43874</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43874</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43880</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>43882</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>43885</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>43892</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>43892</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>43892</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>43899</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>43899</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>43899</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>43899</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>43900</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>43900</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>43900</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>43901</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>43902</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>43903</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>43907</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>43908</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>43909</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>43910</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>43913</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>43913</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>43913</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>43914</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>43915</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>43921</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>43921</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>43924</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>43927</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>43928</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>43930</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>43936</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>43938</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>43938</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>43941</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>43944</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>43944</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>43949</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>43949</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>43949</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>43959</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>43970</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>43999</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>43999</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>43999</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44004</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>44004</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44006</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44007</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>44007</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>44012</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>44015</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>44018</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44031</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>44034</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>44040</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>44041</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>44053</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>44053</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44054</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44055</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>44055</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>44056</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>44062</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44069</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44071</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>44074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>44076</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>44076</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>44076</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>44077</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44084</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>44092</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>44096</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>44099</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44099</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>44105</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44112</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44112</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>44119</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44132</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44132</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44134</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44134</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44144</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44147</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44147</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>44147</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>44152</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>44152</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>44154</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>44155</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>44161</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>44165</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44165</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>44171</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>44172</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>44173</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>44174</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>44176</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44179</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44180</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44183</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44207</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44207</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44209</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44209</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44224</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>44228</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44237</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44242</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44245</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44245</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44245</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44247</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44249</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44249</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44251</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>44252</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>44258</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>44258</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>44258</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>44258</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44264</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>44274</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>44274</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>44277</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>44293</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>44298</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>44300</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44302</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44302</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>44305</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>44305</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>44306</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>44306</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44307</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>44307</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>44309</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>44312</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44321</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44321</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44326</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44333</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44334</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44340</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>44340</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>44340</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>44340</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44341</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44341</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>44343</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>44343</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>44343</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>44348</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44349</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>44349</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>44350</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>44351</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>44356</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>44356</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44357</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44357</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>44357</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>44357</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44363</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>44365</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44367</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>44368</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>44368</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44368</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44369</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>44369</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>44370</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>44371</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>44375</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>44377</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>44377</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44379</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>44382</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44383</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44385</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44385</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>44393</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>44403</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>44412</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27161,7 +27161,7 @@
         <v>44412</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>44412</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>44417</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>44417</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>44417</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>44419</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>44421</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>44428</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44428</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44432</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44433</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44437</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44440</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44441</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>44441</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44441</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44442</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44446</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>44453</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>44453</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44460</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44466</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>44469</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44472</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44475</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44476</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44476</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44476</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44476</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44477</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44480</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44487</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44487</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44487</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44488</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44488</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44488</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44488</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44494</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44495</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44496</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44497</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44497</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44501</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44501</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44504</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44505</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44508</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44508</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44508</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44512</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44513</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44516</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44516</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44518</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44524</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44525</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44525</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44526</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44540</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44544</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44544</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44550</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44552</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44552</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44552</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44558</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44564</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44566</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44571</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44571</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>44572</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>44572</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>44572</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>44572</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>44573</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>44573</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44573</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44573</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>44578</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44578</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44581</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44585</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44585</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44592</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44593</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44594</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44595</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>44596</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>44596</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>44599</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>44599</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>44601</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>44603</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>44608</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>44613</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>44613</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>44613</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>44615</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>44615</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>44616</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33067,7 +33067,7 @@
         <v>44617</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44620</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44621</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44627</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44628</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44629</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44630</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44631</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44634</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44634</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44634</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44637</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44641</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44642</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>44648</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44648</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44648</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44648</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>44649</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>44649</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44649</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44655</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44672</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>44676</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44683</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44685</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44687</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44691</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44692</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>44692</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44692</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44692</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44692</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44698</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>44698</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>44702</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44704</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44704</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>44706</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44706</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44713</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44714</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44714</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44725</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44728</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44742</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44743</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>44749</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44750</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44750</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44750</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44750</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44755</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>44768</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44769</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44776</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44776</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>44776</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44776</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44781</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44788</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>44790</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>44790</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44798</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>44802</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>44806</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44806</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44806</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44810</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44812</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44821</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44826</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44827</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44827</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44827</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44830</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44830</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44831</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44831</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44831</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44832</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44834</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>44834</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>44835</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44838</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>44840</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>44844</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>44851</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>44851</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>44852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>44855</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44858</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44861</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44861</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>44861</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>44866</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>44866</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>44866</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44867</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>44868</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44869</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44874</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44874</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44875</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44876</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44876</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44876</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>44887</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44887</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44888</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>44889</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>44889</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>44889</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>44893</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44894</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44895</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44903</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44904</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>44907</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>44907</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44911</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44911</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44911</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44914</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44916</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>44917</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>44918</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>44928</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>44929</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44929</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44930</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44935</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44935</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44935</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44943</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44943</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44943</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44943</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44944</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44944</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44946</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44951</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44951</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>44951</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44951</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>44953</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>44956</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>44956</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44958</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>44958</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44958</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>44958</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>44965</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>44966</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>44966</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>44966</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>44971</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>44977</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>44978</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>44979</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>44980</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>44981</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>44984</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>44988</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>44993</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44997</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44997</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>44998</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45006</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45007</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45008</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45014</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45015</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45021</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45021</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45021</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45022</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45029</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45030</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45034</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45035</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45040</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45040</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45042</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>45043</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45047</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45049</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45049</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45049</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45050</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45050</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45496,7 +45496,7 @@
         <v>45054</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45553,7 +45553,7 @@
         <v>45054</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>45055</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45060</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45062</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45071</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45071</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45072</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45075</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45075</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45076</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45079</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45079</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45082</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45089</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45090</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45090</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45090</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45091</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>45091</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45091</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45092</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45096</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47092,7 +47092,7 @@
         <v>45097</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47149,7 +47149,7 @@
         <v>45097</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45098</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>45098</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45098</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>45103</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>45104</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45107</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45113</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45114</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>45121</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45124</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>45132</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>45139</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45140</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>45140</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48294,7 +48294,7 @@
         <v>45151</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48351,7 +48351,7 @@
         <v>45151</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>45151</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48465,7 +48465,7 @@
         <v>45151</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>45154</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>45155</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45155</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45162</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45162</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>45167</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45167</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>45167</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45168</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45176</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45176</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45180</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>45180</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>45180</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45181</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>45181</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45182</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45189</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>45195</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49890,7 +49890,7 @@
         <v>45195</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>45196</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>45197</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>45198</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50118,7 +50118,7 @@
         <v>45198</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50175,7 +50175,7 @@
         <v>45198</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50232,7 +50232,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>45201</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50346,7 +50346,7 @@
         <v>45202</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>45202</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45203</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45208</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>45209</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50636,7 +50636,7 @@
         <v>45210</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>45210</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>45210</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45212</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45215</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45217</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45218</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>45218</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51325,7 +51325,7 @@
         <v>45224</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>45226</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>45230</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51496,7 +51496,7 @@
         <v>45230</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>45230</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>45230</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>45232</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>45232</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51774,14 +51774,14 @@
     <row r="875" ht="15" customHeight="1">
       <c r="A875" t="inlineStr">
         <is>
-          <t>A 54590-2023</t>
+          <t>A 54589-2023</t>
         </is>
       </c>
       <c r="B875" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         </is>
       </c>
       <c r="G875" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="H875" t="n">
         <v>0</v>
@@ -51838,7 +51838,7 @@
         <v>45233</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51888,14 +51888,14 @@
     <row r="877" ht="15" customHeight="1">
       <c r="A877" t="inlineStr">
         <is>
-          <t>A 54589-2023</t>
+          <t>A 54590-2023</t>
         </is>
       </c>
       <c r="B877" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51908,7 +51908,7 @@
         </is>
       </c>
       <c r="G877" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="H877" t="n">
         <v>0</v>
@@ -51952,7 +51952,7 @@
         <v>45239</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>45239</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>45243</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52116,14 +52116,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 56385-2023</t>
+          <t>A 56523-2023</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52136,7 +52136,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>6.3</v>
+        <v>1.9</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -52173,14 +52173,14 @@
     <row r="882" ht="15" customHeight="1">
       <c r="A882" t="inlineStr">
         <is>
-          <t>A 56396-2023</t>
+          <t>A 56527-2023</t>
         </is>
       </c>
       <c r="B882" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -52230,14 +52230,14 @@
     <row r="883" ht="15" customHeight="1">
       <c r="A883" t="inlineStr">
         <is>
-          <t>A 56523-2023</t>
+          <t>A 56629-2023</t>
         </is>
       </c>
       <c r="B883" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52250,7 +52250,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>1.9</v>
+        <v>9.6</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -52287,14 +52287,14 @@
     <row r="884" ht="15" customHeight="1">
       <c r="A884" t="inlineStr">
         <is>
-          <t>A 56527-2023</t>
+          <t>A 56385-2023</t>
         </is>
       </c>
       <c r="B884" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52307,7 +52307,7 @@
         </is>
       </c>
       <c r="G884" t="n">
-        <v>3.8</v>
+        <v>6.3</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -52344,14 +52344,14 @@
     <row r="885" ht="15" customHeight="1">
       <c r="A885" t="inlineStr">
         <is>
-          <t>A 56580-2023</t>
+          <t>A 56396-2023</t>
         </is>
       </c>
       <c r="B885" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         </is>
       </c>
       <c r="G885" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H885" t="n">
         <v>0</v>
@@ -52401,14 +52401,14 @@
     <row r="886" ht="15" customHeight="1">
       <c r="A886" t="inlineStr">
         <is>
-          <t>A 56629-2023</t>
+          <t>A 56580-2023</t>
         </is>
       </c>
       <c r="B886" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         </is>
       </c>
       <c r="G886" t="n">
-        <v>9.6</v>
+        <v>1</v>
       </c>
       <c r="H886" t="n">
         <v>0</v>
@@ -52465,7 +52465,7 @@
         <v>45244</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45244</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45250</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>45250</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>45251</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45253</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52810,14 +52810,14 @@
     <row r="893" ht="15" customHeight="1">
       <c r="A893" t="inlineStr">
         <is>
-          <t>A 59979-2023</t>
+          <t>A 59980-2023</t>
         </is>
       </c>
       <c r="B893" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52867,14 +52867,14 @@
     <row r="894" ht="15" customHeight="1">
       <c r="A894" t="inlineStr">
         <is>
-          <t>A 59980-2023</t>
+          <t>A 59979-2023</t>
         </is>
       </c>
       <c r="B894" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45258</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52981,14 +52981,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 60023-2023</t>
+          <t>A 60066-2023</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -53038,14 +53038,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 60066-2023</t>
+          <t>A 60023-2023</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -53102,7 +53102,7 @@
         <v>45260</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45260</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45261</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -564,7 +564,7 @@
         <v>45138</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43644</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>44455</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>44615</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45092</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44505</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>43508</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>43628</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>43970</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44186</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>44613</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>44750</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44866</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44916</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44997</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45184</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45212</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>43573</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>43766</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>44071</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44249</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44417</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>44446</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>44446</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44508</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>44740</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44750</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44750</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>44881</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44889</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45062</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45197</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45229</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45236</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>43314</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43321</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>43336</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>43339</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>43339</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>43339</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>43339</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>43340</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>43348</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>43353</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43353</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43353</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43357</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43357</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43364</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43364</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43376</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>43377</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>43381</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>43383</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>43409</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>43418</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>43420</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>43425</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>43425</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>43427</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>43427</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>43439</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>43446</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>43446</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>43448</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>43452</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>43453</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>43453</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>43453</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>43455</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>43467</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>43468</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>43470</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>43472</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>43474</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>43475</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43475</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43479</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>43479</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>43479</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>43481</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>43482</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>43482</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>43482</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>43486</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>43494</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43495</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>43496</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>43497</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>43497</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43517</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43523</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43534</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>43536</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>43537</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>43538</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>43539</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>43542</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>43544</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>43544</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>43544</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>43544</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>43544</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>43544</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>43550</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>43551</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>43552</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>43556</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>43558</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43560</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>43565</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>43565</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>43565</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>43567</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>43578</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>43579</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>43579</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>43587</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43592</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43593</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43599</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43601</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>43613</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>43613</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>43614</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>43618</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>43618</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>43619</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>43627</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>43633</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43633</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>43635</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>43646</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>43647</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>43648</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>43655</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>43658</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>43670</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>43676</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>43683</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>43690</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>43691</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>43693</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>43693</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>43694</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>43694</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>43696</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>43697</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>43698</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>43698</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>43698</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>43698</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>43700</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>43699</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>43705</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>43707</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>43707</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>43707</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>43709</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>43710</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>43711</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>43712</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>43724</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>43725</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>43731</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>43735</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>43738</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43739</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>43742</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43766</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>43766</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>43766</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>43767</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>43769</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>43769</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>43770</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43774</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43775</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>43777</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>43783</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>43783</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>43784</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43794</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43797</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43797</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>43797</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>43801</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>43803</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>43803</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>43803</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>43805</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>43809</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>43809</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>43811</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>43812</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>43815</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>43815</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>43815</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>43817</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>43817</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>43818</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>43819</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>43837</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>43838</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>43839</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>43846</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>43847</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>43850</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>43854</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>43854</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>43858</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>43859</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>43864</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>43864</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>43864</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43864</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43865</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>43868</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>43868</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>43872</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>43873</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>43873</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43874</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43874</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43880</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>43882</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>43885</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>43892</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>43892</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>43892</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>43899</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>43899</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>43899</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>43899</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>43900</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>43900</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>43900</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>43901</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>43902</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>43903</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>43907</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>43908</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>43909</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>43910</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>43913</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>43913</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>43913</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>43914</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>43915</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>43921</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>43921</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>43924</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>43927</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>43928</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>43930</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>43936</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>43938</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>43938</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>43941</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>43944</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>43944</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>43949</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>43949</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>43949</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>43959</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>43970</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>43999</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>43999</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>43999</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44004</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>44004</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44006</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44007</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>44007</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>44012</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>44015</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>44018</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44031</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>44034</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>44040</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>44041</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>44053</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>44053</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44054</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44055</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>44055</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>44056</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>44062</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44069</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44071</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>44074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>44076</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>44076</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>44076</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>44077</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44084</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>44092</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>44096</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>44099</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44099</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>44105</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44112</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44112</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>44119</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44132</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44132</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44134</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44134</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44144</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44147</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44147</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>44147</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>44152</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>44152</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>44154</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>44155</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>44161</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>44165</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44165</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>44171</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>44172</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>44173</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>44174</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>44176</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44179</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44180</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44183</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44207</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44207</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44209</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44209</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44224</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>44228</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44237</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44242</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44245</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44245</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44245</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44247</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44249</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44249</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44251</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>44252</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>44258</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>44258</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>44258</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>44258</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44264</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>44274</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>44274</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>44277</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>44293</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>44298</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>44300</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44302</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44302</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>44305</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>44305</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>44306</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>44306</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44307</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>44307</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>44309</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>44312</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44321</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44321</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44326</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44333</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44334</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44340</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>44340</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>44340</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>44340</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44341</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44341</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>44343</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>44343</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>44343</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>44348</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44349</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>44349</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>44350</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>44351</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>44356</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>44356</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44357</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44357</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>44357</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>44357</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44363</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>44365</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44367</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>44368</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>44368</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44368</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44369</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>44369</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>44370</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>44371</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>44375</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>44377</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>44377</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44379</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>44382</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44383</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44385</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44385</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>44393</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>44403</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>44412</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27161,7 +27161,7 @@
         <v>44412</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>44412</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>44417</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>44417</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>44417</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>44419</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>44421</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>44428</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44428</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44432</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44433</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44437</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44440</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44441</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>44441</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44441</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44442</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44446</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>44453</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>44453</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44460</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44466</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>44469</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44472</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44475</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44476</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44476</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44476</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44476</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44477</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44480</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44487</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44487</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44487</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44488</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44488</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44488</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44488</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44494</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44495</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44496</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44497</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44497</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44501</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44501</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44504</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44505</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44508</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44508</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44508</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44512</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44513</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44516</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44516</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44518</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44524</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44525</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44525</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44526</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44540</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44544</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44544</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44550</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44552</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44552</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44552</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44558</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44564</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44566</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44571</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44571</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>44572</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>44572</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>44572</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>44572</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>44573</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>44573</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44573</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44573</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>44578</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44578</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44581</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44585</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44585</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44592</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44593</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44594</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44595</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>44596</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>44596</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>44599</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>44599</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>44601</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>44603</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>44608</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>44613</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>44613</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>44613</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>44615</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>44615</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>44616</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33067,7 +33067,7 @@
         <v>44617</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44620</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44621</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44627</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44628</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44629</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44630</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44631</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44634</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44634</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44634</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44637</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44641</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44642</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>44648</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44648</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44648</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44648</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>44649</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>44649</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44649</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44655</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44672</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>44676</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44683</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44685</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44687</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44691</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44692</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>44692</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44692</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44692</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44692</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44698</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>44698</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>44702</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44704</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44704</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>44706</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44706</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44713</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44714</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44714</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44725</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44728</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44742</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44743</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>44749</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44750</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44750</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44750</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44750</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44755</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>44768</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44769</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44776</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44776</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>44776</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44776</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44781</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44788</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>44790</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>44790</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44798</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>44802</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>44806</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44806</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44806</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44810</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44812</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44821</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44826</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44827</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44827</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44827</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44830</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44830</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44831</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44831</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44831</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44832</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44834</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>44834</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>44835</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44838</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>44840</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>44844</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>44851</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>44851</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>44852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>44855</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44858</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44861</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44861</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>44861</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>44866</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>44866</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>44866</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44867</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>44868</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44869</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44874</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44874</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44875</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44876</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44876</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44876</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>44887</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44887</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44888</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>44889</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>44889</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>44889</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>44893</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44894</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44895</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44903</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44904</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>44907</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>44907</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44911</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44911</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44911</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44914</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44916</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>44917</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>44918</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>44928</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>44929</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44929</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44930</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44935</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44935</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44935</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44943</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44943</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44943</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44943</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44944</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44944</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44946</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44951</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44951</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>44951</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44951</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>44953</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>44956</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>44956</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44958</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>44958</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44958</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>44958</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>44965</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>44966</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>44966</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>44966</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>44971</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>44977</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>44978</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>44979</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>44980</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>44981</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>44984</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>44988</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>44993</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44997</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44997</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>44998</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45006</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45007</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45008</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45014</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45015</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45021</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45021</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45021</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45022</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45029</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45030</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45034</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45035</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45040</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45040</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45042</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>45043</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45047</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45049</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45049</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45049</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45050</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45050</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45496,7 +45496,7 @@
         <v>45054</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45553,7 +45553,7 @@
         <v>45054</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>45055</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45060</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45062</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45071</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45071</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45072</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45075</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45075</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45076</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45079</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45079</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45082</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45089</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45090</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45090</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45090</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45091</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>45091</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45091</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45092</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45096</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47092,7 +47092,7 @@
         <v>45097</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47149,7 +47149,7 @@
         <v>45097</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45098</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>45098</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45098</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>45103</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>45104</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45107</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45113</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45114</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>45121</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45124</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>45132</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>45139</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45140</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>45140</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48294,7 +48294,7 @@
         <v>45151</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48351,7 +48351,7 @@
         <v>45151</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>45151</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48465,7 +48465,7 @@
         <v>45151</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>45154</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>45155</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45155</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45162</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45162</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>45167</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45167</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>45167</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45168</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45176</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45176</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45180</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>45180</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>45180</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45181</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>45181</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45182</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45189</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>45195</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49890,7 +49890,7 @@
         <v>45195</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>45196</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>45197</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>45198</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50118,7 +50118,7 @@
         <v>45198</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50175,7 +50175,7 @@
         <v>45198</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50232,7 +50232,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>45201</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50346,7 +50346,7 @@
         <v>45202</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>45202</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45203</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45208</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>45209</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50636,7 +50636,7 @@
         <v>45210</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>45210</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>45210</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45212</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45215</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45217</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45218</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>45218</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51325,7 +51325,7 @@
         <v>45224</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>45226</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>45230</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51496,7 +51496,7 @@
         <v>45230</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>45230</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>45230</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>45232</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>45232</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>45233</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>45233</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45233</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51945,14 +51945,14 @@
     <row r="878" ht="15" customHeight="1">
       <c r="A878" t="inlineStr">
         <is>
-          <t>A 55819-2023</t>
+          <t>A 55700-2023</t>
         </is>
       </c>
       <c r="B878" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -51965,7 +51965,7 @@
         </is>
       </c>
       <c r="G878" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H878" t="n">
         <v>0</v>
@@ -52002,14 +52002,14 @@
     <row r="879" ht="15" customHeight="1">
       <c r="A879" t="inlineStr">
         <is>
-          <t>A 55700-2023</t>
+          <t>A 55819-2023</t>
         </is>
       </c>
       <c r="B879" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52022,7 +52022,7 @@
         </is>
       </c>
       <c r="G879" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H879" t="n">
         <v>0</v>
@@ -52066,7 +52066,7 @@
         <v>45243</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>45243</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52180,7 +52180,7 @@
         <v>45243</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52237,7 +52237,7 @@
         <v>45243</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52294,7 +52294,7 @@
         <v>45243</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52351,7 +52351,7 @@
         <v>45243</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>45243</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>45244</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45244</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45250</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>45250</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>45251</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45253</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45257</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45257</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45258</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45258</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45258</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53095,14 +53095,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 60679-2023</t>
+          <t>A 60739-2023</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -53152,14 +53152,14 @@
     <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 60739-2023</t>
+          <t>A 60679-2023</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53172,7 +53172,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -53216,7 +53216,7 @@
         <v>45261</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y900"/>
+  <dimension ref="A1:Y901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>45138</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43644</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>44455</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>44615</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45092</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44505</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>43508</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>43628</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>43970</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44186</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>44613</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>44750</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44866</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44916</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44997</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45184</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45212</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>43573</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>43766</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>44071</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44249</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44417</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>44446</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>44446</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44508</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>44740</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44750</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44750</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>44881</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44889</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45062</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45197</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45229</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45236</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>43314</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43321</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>43336</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>43339</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>43339</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>43339</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>43339</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>43340</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>43348</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>43353</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43353</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43353</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43357</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43357</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43364</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43364</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43376</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>43377</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>43381</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>43383</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>43409</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>43418</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>43420</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>43425</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>43425</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>43427</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>43427</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>43439</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>43446</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>43446</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>43448</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>43452</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>43453</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>43453</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>43453</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>43455</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>43467</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>43468</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>43470</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>43472</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>43474</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>43475</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43475</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43479</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>43479</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>43479</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>43481</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>43482</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>43482</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>43482</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>43486</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>43494</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43495</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>43496</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>43497</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>43497</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43517</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43523</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43534</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>43536</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>43537</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>43538</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>43539</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>43542</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>43544</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>43544</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>43544</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>43544</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>43544</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>43544</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>43550</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>43551</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>43552</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>43556</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>43558</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43560</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>43565</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>43565</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>43565</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>43567</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>43578</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>43579</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>43579</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>43587</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43592</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43593</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43599</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43601</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>43613</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>43613</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>43614</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>43618</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>43618</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>43619</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>43627</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>43633</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43633</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>43635</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>43646</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>43647</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>43648</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>43655</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>43658</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>43670</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>43676</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>43683</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>43690</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>43691</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>43693</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>43693</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>43694</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>43694</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>43696</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>43697</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>43698</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>43698</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>43698</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>43698</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>43700</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>43699</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>43705</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>43707</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>43707</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>43707</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>43709</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>43710</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>43711</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>43712</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>43724</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>43725</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>43731</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>43735</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>43738</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43739</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>43742</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43766</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>43766</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>43766</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>43767</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>43769</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>43769</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>43770</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43774</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43775</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>43777</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>43783</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>43783</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>43784</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43794</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43797</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43797</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>43797</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>43801</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>43803</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>43803</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>43803</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>43805</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>43809</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>43809</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>43811</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>43812</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>43815</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>43815</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>43815</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>43817</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>43817</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>43818</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>43819</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>43837</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>43838</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>43839</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>43846</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>43847</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>43850</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>43854</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>43854</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>43858</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>43859</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>43864</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>43864</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>43864</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43864</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43865</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>43868</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>43868</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>43872</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>43873</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>43873</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43874</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43874</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43880</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>43882</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>43885</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>43892</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>43892</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>43892</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>43899</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>43899</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>43899</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>43899</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>43900</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>43900</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>43900</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>43901</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>43902</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>43903</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>43907</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>43908</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>43909</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>43910</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>43913</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>43913</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>43913</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>43914</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>43915</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>43921</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>43921</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>43924</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>43927</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>43928</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>43930</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>43936</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>43938</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>43938</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>43941</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>43944</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>43944</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>43949</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>43949</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>43949</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>43959</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>43970</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>43999</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>43999</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>43999</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44004</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>44004</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44006</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44007</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>44007</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>44012</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>44015</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>44018</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44031</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>44034</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>44040</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>44041</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>44053</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>44053</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44054</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44055</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>44055</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>44056</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>44062</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44069</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44071</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>44074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>44076</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>44076</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>44076</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>44077</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44084</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>44092</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>44096</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>44099</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44099</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>44105</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44112</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44112</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>44119</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44132</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44132</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44134</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44134</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44144</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44147</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44147</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>44147</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>44152</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>44152</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>44154</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>44155</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>44161</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>44165</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44165</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>44171</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>44172</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>44173</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>44174</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>44176</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44179</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44180</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44183</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44207</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44207</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44209</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44209</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44224</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>44228</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44237</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44242</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44245</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44245</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44245</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44247</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44249</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44249</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44251</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>44252</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>44258</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>44258</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>44258</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>44258</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44264</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>44274</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>44274</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>44277</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>44293</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>44298</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>44300</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44302</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44302</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>44305</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>44305</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>44306</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>44306</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44307</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>44307</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>44309</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>44312</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44321</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44321</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44326</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44333</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44334</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44340</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>44340</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>44340</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>44340</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44341</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44341</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>44343</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>44343</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>44343</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>44348</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44349</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>44349</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>44350</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>44351</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>44356</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>44356</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44357</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44357</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>44357</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>44357</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44363</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>44365</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44367</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>44368</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>44368</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44368</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44369</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>44369</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>44370</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>44371</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>44375</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>44377</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>44377</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44379</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>44382</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44383</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44385</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44385</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>44393</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>44403</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>44412</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27161,7 +27161,7 @@
         <v>44412</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>44412</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>44417</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>44417</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>44417</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>44419</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>44421</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>44428</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44428</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44432</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44433</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44437</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44440</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44441</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>44441</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44441</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44442</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44446</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>44453</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>44453</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44460</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44466</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>44469</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44472</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44475</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44476</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44476</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44476</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44476</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44477</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44480</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44487</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44487</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44487</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44488</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44488</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44488</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44488</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44494</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44495</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44496</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44497</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44497</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44501</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44501</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44504</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44505</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44508</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44508</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44508</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44512</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44513</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44516</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44516</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44518</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44524</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44525</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44525</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44526</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44540</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44544</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44544</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44550</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44552</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44552</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44552</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44558</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44564</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44566</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44571</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44571</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>44572</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>44572</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>44572</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>44572</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>44573</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>44573</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44573</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44573</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>44578</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44578</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44581</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44585</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44585</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44592</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44593</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44594</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44595</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>44596</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>44596</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>44599</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>44599</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>44601</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>44603</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>44608</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>44613</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>44613</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>44613</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>44615</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>44615</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>44616</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33067,7 +33067,7 @@
         <v>44617</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44620</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44621</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44627</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44628</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44629</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44630</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44631</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44634</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44634</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44634</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44637</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44641</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44642</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>44648</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44648</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44648</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44648</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>44649</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>44649</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44649</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44655</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44672</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>44676</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44683</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44685</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44687</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44691</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44692</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>44692</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44692</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44692</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44692</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44698</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>44698</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>44702</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44704</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44704</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>44706</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44706</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44713</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44714</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44714</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44725</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44728</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44742</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44743</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>44749</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44750</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44750</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44750</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44750</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44755</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>44768</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44769</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44776</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44776</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>44776</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44776</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44781</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44788</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>44790</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>44790</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44798</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>44802</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>44806</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44806</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44806</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44810</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44812</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44821</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44826</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44827</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44827</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44827</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44830</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44830</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44831</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44831</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44831</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44832</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44834</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>44834</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>44835</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44838</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>44840</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>44844</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>44851</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>44851</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>44852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>44855</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44858</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44861</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44861</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>44861</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>44866</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>44866</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>44866</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44867</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>44868</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44869</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44874</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44874</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44875</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44876</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44876</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44876</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>44887</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44887</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44888</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>44889</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>44889</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>44889</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>44893</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44894</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44895</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44903</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44904</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>44907</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>44907</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44911</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44911</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44911</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44914</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44916</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>44917</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>44918</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>44928</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>44929</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44929</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44930</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44935</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44935</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44935</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44943</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44943</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44943</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44943</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44944</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44944</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44946</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44951</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44951</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>44951</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44951</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>44953</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>44956</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>44956</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44958</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>44958</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44958</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>44958</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>44965</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>44966</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>44966</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>44966</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>44971</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>44977</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>44978</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>44979</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>44980</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>44981</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>44984</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>44988</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>44993</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44997</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44997</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>44998</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45006</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45007</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45008</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45014</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45015</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45021</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45021</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45021</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45022</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45029</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45030</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45034</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45035</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45040</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45040</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45042</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>45043</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45047</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45049</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45049</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45049</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45050</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45050</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45496,7 +45496,7 @@
         <v>45054</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45553,7 +45553,7 @@
         <v>45054</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>45055</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45060</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45062</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45071</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45071</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45072</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45075</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45075</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45076</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45079</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45079</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45082</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45089</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45090</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45090</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45090</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45091</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>45091</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45091</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45092</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45096</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47092,7 +47092,7 @@
         <v>45097</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47149,7 +47149,7 @@
         <v>45097</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45098</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>45098</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45098</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>45103</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>45104</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45107</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45113</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45114</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>45121</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45124</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>45132</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>45139</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45140</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>45140</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48294,7 +48294,7 @@
         <v>45151</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48351,7 +48351,7 @@
         <v>45151</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>45151</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48465,7 +48465,7 @@
         <v>45151</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>45154</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>45155</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45155</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45162</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45162</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>45167</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45167</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>45167</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45168</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45176</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45176</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45180</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>45180</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>45180</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45181</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>45181</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45182</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45189</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>45195</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49890,7 +49890,7 @@
         <v>45195</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>45196</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>45197</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>45198</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50118,7 +50118,7 @@
         <v>45198</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50175,7 +50175,7 @@
         <v>45198</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50232,7 +50232,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>45201</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50346,7 +50346,7 @@
         <v>45202</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>45202</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45203</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45208</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>45209</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50636,7 +50636,7 @@
         <v>45210</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>45210</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>45210</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45212</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45215</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45217</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45218</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>45218</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51325,7 +51325,7 @@
         <v>45224</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>45226</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>45230</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51496,7 +51496,7 @@
         <v>45230</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>45230</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>45230</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>45232</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>45232</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>45233</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>45233</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45233</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>45239</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>45239</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52059,14 +52059,14 @@
     <row r="880" ht="15" customHeight="1">
       <c r="A880" t="inlineStr">
         <is>
-          <t>A 56381-2023</t>
+          <t>A 56385-2023</t>
         </is>
       </c>
       <c r="B880" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52079,7 +52079,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>0.4</v>
+        <v>6.3</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -52116,14 +52116,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 56523-2023</t>
+          <t>A 56396-2023</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52136,7 +52136,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>1.9</v>
+        <v>9</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -52173,14 +52173,14 @@
     <row r="882" ht="15" customHeight="1">
       <c r="A882" t="inlineStr">
         <is>
-          <t>A 56527-2023</t>
+          <t>A 56580-2023</t>
         </is>
       </c>
       <c r="B882" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -52230,14 +52230,14 @@
     <row r="883" ht="15" customHeight="1">
       <c r="A883" t="inlineStr">
         <is>
-          <t>A 56629-2023</t>
+          <t>A 56381-2023</t>
         </is>
       </c>
       <c r="B883" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52250,7 +52250,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>9.6</v>
+        <v>0.4</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -52287,14 +52287,14 @@
     <row r="884" ht="15" customHeight="1">
       <c r="A884" t="inlineStr">
         <is>
-          <t>A 56385-2023</t>
+          <t>A 56523-2023</t>
         </is>
       </c>
       <c r="B884" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52307,7 +52307,7 @@
         </is>
       </c>
       <c r="G884" t="n">
-        <v>6.3</v>
+        <v>1.9</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -52344,14 +52344,14 @@
     <row r="885" ht="15" customHeight="1">
       <c r="A885" t="inlineStr">
         <is>
-          <t>A 56396-2023</t>
+          <t>A 56527-2023</t>
         </is>
       </c>
       <c r="B885" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         </is>
       </c>
       <c r="G885" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="H885" t="n">
         <v>0</v>
@@ -52401,14 +52401,14 @@
     <row r="886" ht="15" customHeight="1">
       <c r="A886" t="inlineStr">
         <is>
-          <t>A 56580-2023</t>
+          <t>A 56629-2023</t>
         </is>
       </c>
       <c r="B886" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         </is>
       </c>
       <c r="G886" t="n">
-        <v>1</v>
+        <v>9.6</v>
       </c>
       <c r="H886" t="n">
         <v>0</v>
@@ -52465,7 +52465,7 @@
         <v>45244</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45244</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45250</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>45250</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>45251</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45253</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52810,14 +52810,14 @@
     <row r="893" ht="15" customHeight="1">
       <c r="A893" t="inlineStr">
         <is>
-          <t>A 59980-2023</t>
+          <t>A 59979-2023</t>
         </is>
       </c>
       <c r="B893" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52867,14 +52867,14 @@
     <row r="894" ht="15" customHeight="1">
       <c r="A894" t="inlineStr">
         <is>
-          <t>A 59979-2023</t>
+          <t>A 59980-2023</t>
         </is>
       </c>
       <c r="B894" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52924,14 +52924,14 @@
     <row r="895" ht="15" customHeight="1">
       <c r="A895" t="inlineStr">
         <is>
-          <t>A 60177-2023</t>
+          <t>A 60023-2023</t>
         </is>
       </c>
       <c r="B895" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         </is>
       </c>
       <c r="G895" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="H895" t="n">
         <v>0</v>
@@ -52988,7 +52988,7 @@
         <v>45258</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53038,14 +53038,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 60023-2023</t>
+          <t>A 60177-2023</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -53095,14 +53095,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 60739-2023</t>
+          <t>A 60679-2023</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -53152,14 +53152,14 @@
     <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 60679-2023</t>
+          <t>A 60739-2023</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53172,7 +53172,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -53206,7 +53206,7 @@
       </c>
       <c r="R899" s="2" t="inlineStr"/>
     </row>
-    <row r="900">
+    <row r="900" ht="15" customHeight="1">
       <c r="A900" t="inlineStr">
         <is>
           <t>A 60909-2023</t>
@@ -53216,7 +53216,7 @@
         <v>45261</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45264</v>
+        <v>45265</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53262,6 +53262,63 @@
         <v>0</v>
       </c>
       <c r="R900" s="2" t="inlineStr"/>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>A 61334-2023</t>
+        </is>
+      </c>
+      <c r="B901" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="C901" s="1" t="n">
+        <v>45265</v>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>BENGTSFORS</t>
+        </is>
+      </c>
+      <c r="G901" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H901" t="n">
+        <v>0</v>
+      </c>
+      <c r="I901" t="n">
+        <v>0</v>
+      </c>
+      <c r="J901" t="n">
+        <v>0</v>
+      </c>
+      <c r="K901" t="n">
+        <v>0</v>
+      </c>
+      <c r="L901" t="n">
+        <v>0</v>
+      </c>
+      <c r="M901" t="n">
+        <v>0</v>
+      </c>
+      <c r="N901" t="n">
+        <v>0</v>
+      </c>
+      <c r="O901" t="n">
+        <v>0</v>
+      </c>
+      <c r="P901" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q901" t="n">
+        <v>0</v>
+      </c>
+      <c r="R901" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -564,7 +564,7 @@
         <v>45138</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43644</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>44455</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>44615</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45092</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44505</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>43508</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>43628</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>43970</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44186</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>44613</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>44750</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44866</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44916</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44997</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45184</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45212</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>43573</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>43766</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>44071</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44249</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44417</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>44446</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>44446</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44508</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>44740</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44750</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44750</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>44881</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44889</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45062</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45197</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45229</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45236</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>43314</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43321</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>43336</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>43339</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>43339</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>43339</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>43339</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>43340</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>43348</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>43353</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43353</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43353</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43357</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43357</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43364</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43364</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43376</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>43377</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>43381</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>43383</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>43409</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>43418</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>43420</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>43425</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>43425</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>43427</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>43427</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>43439</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>43446</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>43446</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>43448</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>43452</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>43453</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>43453</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>43453</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>43455</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>43467</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>43468</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>43470</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>43472</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>43474</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>43475</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43475</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43479</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>43479</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>43479</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>43481</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>43482</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>43482</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>43482</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>43486</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>43494</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43495</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>43496</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>43497</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>43497</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43517</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43523</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43534</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>43536</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>43537</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>43538</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>43539</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>43542</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>43544</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>43544</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>43544</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>43544</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>43544</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>43544</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>43550</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>43551</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>43552</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>43556</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>43558</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43560</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>43565</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>43565</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>43565</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>43567</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>43578</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>43579</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>43579</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>43587</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43592</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43593</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43599</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43601</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>43613</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>43613</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>43614</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>43618</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>43618</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>43619</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>43627</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>43633</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43633</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>43635</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>43646</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>43647</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>43648</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>43655</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>43658</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>43670</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>43676</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>43683</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>43690</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>43691</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>43693</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>43693</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>43694</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>43694</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>43696</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>43697</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>43698</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>43698</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>43698</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>43698</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>43700</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>43699</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>43705</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>43707</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>43707</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>43707</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>43709</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>43710</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>43711</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>43712</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>43724</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>43725</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>43731</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>43735</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>43738</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43739</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>43742</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43766</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>43766</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>43766</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>43767</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>43769</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>43769</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>43770</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43774</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43775</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>43777</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>43783</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>43783</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>43784</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43794</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43797</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43797</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>43797</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>43801</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>43803</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>43803</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>43803</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>43805</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>43809</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>43809</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>43811</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>43812</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>43815</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>43815</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>43815</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>43817</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>43817</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>43818</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>43819</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>43837</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>43838</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>43839</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>43846</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>43847</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>43850</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>43854</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>43854</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>43858</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>43859</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>43864</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>43864</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>43864</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43864</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43865</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>43868</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>43868</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>43872</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>43873</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>43873</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43874</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43874</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43880</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>43882</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>43885</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>43892</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>43892</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>43892</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>43899</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>43899</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>43899</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>43899</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>43900</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>43900</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>43900</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>43901</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>43902</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>43903</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>43907</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>43908</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>43909</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>43910</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>43913</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>43913</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>43913</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>43914</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>43915</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>43921</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>43921</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>43924</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>43927</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>43928</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>43930</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>43936</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>43938</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>43938</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>43941</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>43944</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>43944</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>43949</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>43949</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>43949</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>43959</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>43970</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>43999</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>43999</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>43999</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44004</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>44004</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44006</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44007</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>44007</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>44012</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>44015</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>44018</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44031</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>44034</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>44040</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>44041</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>44053</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>44053</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44054</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44055</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>44055</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>44056</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>44062</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44069</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44071</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>44074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>44076</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>44076</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>44076</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>44077</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44084</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>44092</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>44096</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>44099</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44099</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>44105</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44112</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44112</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>44119</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44132</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44132</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44134</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44134</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44144</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44147</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44147</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>44147</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>44152</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>44152</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>44154</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>44155</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>44161</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>44165</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44165</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>44171</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>44172</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>44173</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>44174</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>44176</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44179</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44180</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44183</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44207</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44207</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44209</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44209</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44224</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>44228</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44237</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44242</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44245</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44245</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44245</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44247</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44249</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44249</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44251</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>44252</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>44258</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>44258</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>44258</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>44258</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44264</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>44274</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>44274</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>44277</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>44293</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>44298</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>44300</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44302</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44302</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>44305</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>44305</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>44306</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>44306</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44307</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>44307</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>44309</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>44312</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44321</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44321</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44326</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44333</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44334</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44340</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>44340</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>44340</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>44340</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44341</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44341</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>44343</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>44343</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>44343</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>44348</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44349</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>44349</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>44350</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>44351</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>44356</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>44356</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44357</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44357</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>44357</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>44357</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44363</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>44365</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44367</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>44368</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>44368</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44368</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44369</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>44369</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>44370</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>44371</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>44375</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>44377</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>44377</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44379</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>44382</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44383</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44385</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44385</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>44393</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>44403</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>44412</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27161,7 +27161,7 @@
         <v>44412</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>44412</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>44417</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>44417</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>44417</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>44419</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>44421</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>44428</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44428</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44432</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44433</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44437</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44440</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44441</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>44441</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44441</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44442</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44446</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>44453</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>44453</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44460</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44466</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>44469</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44472</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44475</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44476</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44476</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44476</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44476</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44477</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44480</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44487</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44487</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44487</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44488</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44488</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44488</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44488</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44494</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44495</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44496</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44497</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44497</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44501</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44501</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44504</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44505</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44508</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44508</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44508</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44512</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44513</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44516</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44516</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44518</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44524</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44525</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44525</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44526</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44540</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44544</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44544</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44550</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44552</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44552</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44552</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44558</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44564</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44566</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44571</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44571</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>44572</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>44572</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>44572</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>44572</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>44573</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>44573</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44573</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44573</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>44578</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44578</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44581</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44585</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44585</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44592</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44593</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44594</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44595</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>44596</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>44596</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>44599</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>44599</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>44601</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>44603</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>44608</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>44613</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>44613</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>44613</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>44615</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>44615</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>44616</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33067,7 +33067,7 @@
         <v>44617</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44620</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44621</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44627</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44628</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44629</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44630</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44631</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44634</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44634</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44634</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44637</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44641</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44642</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>44648</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44648</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44648</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44648</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>44649</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>44649</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44649</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44655</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44672</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>44676</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44683</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44685</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44687</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44691</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44692</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>44692</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44692</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44692</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44692</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44698</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>44698</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>44702</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44704</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44704</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>44706</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44706</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44713</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44714</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44714</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44725</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44728</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44742</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44743</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>44749</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44750</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44750</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44750</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44750</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44755</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>44768</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44769</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44776</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44776</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>44776</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44776</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44781</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44788</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>44790</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>44790</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44798</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>44802</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>44806</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44806</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44806</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44810</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44812</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44821</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44826</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44827</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44827</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44827</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44830</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44830</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44831</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44831</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44831</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44832</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44834</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>44834</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>44835</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44838</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>44840</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>44844</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>44851</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>44851</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>44852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>44855</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44858</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44861</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44861</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>44861</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>44866</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>44866</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>44866</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44867</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>44868</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44869</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44874</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44874</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44875</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44876</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44876</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44876</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>44887</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44887</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44888</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>44889</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>44889</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>44889</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>44893</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44894</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44895</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44903</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44904</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>44907</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>44907</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44911</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44911</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44911</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44914</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44916</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>44917</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>44918</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>44928</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>44929</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44929</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44930</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44935</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44935</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44935</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44943</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44943</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44943</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44943</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44944</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44944</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44946</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44951</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44951</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>44951</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44951</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>44953</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>44956</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>44956</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44958</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>44958</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44958</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>44958</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>44965</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>44966</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>44966</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>44966</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>44971</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>44977</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>44978</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>44979</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>44980</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>44981</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>44984</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>44988</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>44993</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44997</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44997</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>44998</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45006</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45007</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45008</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45014</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45015</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45021</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45021</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45021</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45022</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45029</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45030</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45034</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45035</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45040</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45040</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45042</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>45043</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45047</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45049</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45049</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45049</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45050</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45050</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45496,7 +45496,7 @@
         <v>45054</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45553,7 +45553,7 @@
         <v>45054</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>45055</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45060</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45062</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45071</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45071</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45072</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45075</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45075</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45076</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45079</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45079</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45082</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45089</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45090</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45090</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45090</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45091</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>45091</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45091</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45092</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45096</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47092,7 +47092,7 @@
         <v>45097</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47149,7 +47149,7 @@
         <v>45097</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45098</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>45098</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45098</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>45103</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>45104</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45107</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45113</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45114</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>45121</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45124</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>45132</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>45139</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45140</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>45140</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48294,7 +48294,7 @@
         <v>45151</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48351,7 +48351,7 @@
         <v>45151</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>45151</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48465,7 +48465,7 @@
         <v>45151</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>45154</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>45155</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45155</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45162</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45162</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>45167</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45167</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>45167</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45168</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45176</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45176</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45180</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>45180</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>45180</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45181</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>45181</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45182</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45189</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>45195</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49890,7 +49890,7 @@
         <v>45195</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>45196</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>45197</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>45198</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50118,7 +50118,7 @@
         <v>45198</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50175,7 +50175,7 @@
         <v>45198</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50232,7 +50232,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>45201</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50346,7 +50346,7 @@
         <v>45202</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>45202</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45203</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45208</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>45209</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50636,7 +50636,7 @@
         <v>45210</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>45210</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>45210</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45212</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45215</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45217</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45218</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>45218</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51325,7 +51325,7 @@
         <v>45224</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>45226</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>45230</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51496,7 +51496,7 @@
         <v>45230</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>45230</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>45230</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>45232</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>45232</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>45233</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>45233</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45233</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>45239</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>45239</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>45243</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>45243</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52180,7 +52180,7 @@
         <v>45243</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52237,7 +52237,7 @@
         <v>45243</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52294,7 +52294,7 @@
         <v>45243</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52351,7 +52351,7 @@
         <v>45243</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>45243</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52458,14 +52458,14 @@
     <row r="887" ht="15" customHeight="1">
       <c r="A887" t="inlineStr">
         <is>
-          <t>A 56735-2023</t>
+          <t>A 56733-2023</t>
         </is>
       </c>
       <c r="B887" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52478,7 +52478,7 @@
         </is>
       </c>
       <c r="G887" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="H887" t="n">
         <v>0</v>
@@ -52515,14 +52515,14 @@
     <row r="888" ht="15" customHeight="1">
       <c r="A888" t="inlineStr">
         <is>
-          <t>A 56733-2023</t>
+          <t>A 56735-2023</t>
         </is>
       </c>
       <c r="B888" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52535,7 +52535,7 @@
         </is>
       </c>
       <c r="G888" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>
@@ -52579,7 +52579,7 @@
         <v>45250</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>45250</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>45251</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45253</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52810,14 +52810,14 @@
     <row r="893" ht="15" customHeight="1">
       <c r="A893" t="inlineStr">
         <is>
-          <t>A 59979-2023</t>
+          <t>A 59980-2023</t>
         </is>
       </c>
       <c r="B893" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52867,14 +52867,14 @@
     <row r="894" ht="15" customHeight="1">
       <c r="A894" t="inlineStr">
         <is>
-          <t>A 59980-2023</t>
+          <t>A 59979-2023</t>
         </is>
       </c>
       <c r="B894" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45258</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52981,14 +52981,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 60066-2023</t>
+          <t>A 60177-2023</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -53038,14 +53038,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 60177-2023</t>
+          <t>A 60066-2023</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -53102,7 +53102,7 @@
         <v>45260</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45260</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45261</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45264</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -564,7 +564,7 @@
         <v>45138</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43644</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>44455</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>44615</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45092</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44505</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>43508</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>43628</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>43970</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44186</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>44613</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>44750</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44866</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44916</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44997</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45184</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45212</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>43573</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>43766</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>44071</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44249</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44417</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>44446</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>44446</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44508</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>44740</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44750</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44750</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>44881</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44889</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45062</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45197</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45229</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45236</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>43314</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43321</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>43336</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>43339</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>43339</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>43339</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>43339</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>43340</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>43348</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>43353</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43353</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43353</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43357</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43357</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43364</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43364</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43376</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>43377</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>43381</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>43383</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>43409</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>43418</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>43420</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>43425</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>43425</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>43427</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>43427</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>43439</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>43446</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>43446</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>43448</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>43452</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>43453</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>43453</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>43453</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>43455</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>43467</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>43468</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>43470</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>43472</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>43474</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>43475</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43475</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43479</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>43479</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>43479</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>43481</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>43482</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>43482</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>43482</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>43486</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>43494</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43495</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>43496</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>43497</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>43497</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43517</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43523</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43534</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>43536</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>43537</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>43538</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>43539</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>43542</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>43544</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>43544</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>43544</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>43544</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>43544</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>43544</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>43550</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>43551</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>43552</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>43556</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>43558</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43560</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>43565</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>43565</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>43565</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>43567</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>43578</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>43579</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>43579</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>43587</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43592</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43593</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43599</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43601</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>43613</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>43613</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>43614</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>43618</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>43618</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>43619</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>43627</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>43633</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43633</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>43635</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>43646</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>43647</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>43648</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>43655</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>43658</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>43670</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>43676</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>43683</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>43690</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>43691</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>43693</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>43693</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>43694</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>43694</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>43696</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>43697</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>43698</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>43698</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>43698</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>43698</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>43700</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>43699</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>43705</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>43707</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>43707</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>43707</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>43709</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>43710</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>43711</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>43712</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>43724</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>43725</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>43731</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>43735</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>43738</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43739</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>43742</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43766</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>43766</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>43766</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>43767</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>43769</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>43769</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>43770</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43774</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43775</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>43777</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>43783</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>43783</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>43784</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43794</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43797</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43797</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>43797</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>43801</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>43803</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>43803</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>43803</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>43805</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>43809</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>43809</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>43811</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>43812</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>43815</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>43815</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>43815</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>43817</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>43817</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>43818</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>43819</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>43837</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>43838</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>43839</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>43846</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>43847</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>43850</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>43854</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>43854</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>43858</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>43859</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>43864</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>43864</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>43864</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43864</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43865</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>43868</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>43868</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>43872</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>43873</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>43873</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43874</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43874</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43880</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>43882</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>43885</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>43892</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>43892</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>43892</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>43899</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>43899</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>43899</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>43899</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>43900</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>43900</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>43900</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>43901</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>43902</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>43903</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>43907</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>43908</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>43909</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>43910</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>43913</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>43913</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>43913</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>43914</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>43915</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>43921</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>43921</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>43924</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>43927</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>43928</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>43930</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>43936</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>43938</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>43938</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>43941</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>43944</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>43944</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>43949</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>43949</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>43949</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>43959</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>43970</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>43999</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>43999</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>43999</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44004</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>44004</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44006</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44007</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>44007</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>44012</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>44015</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>44018</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44031</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>44034</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>44040</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>44041</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>44053</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>44053</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44054</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44055</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>44055</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>44056</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>44062</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44069</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44071</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>44074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>44076</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>44076</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>44076</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>44077</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44084</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>44092</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>44096</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>44099</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44099</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>44105</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44112</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44112</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>44119</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44132</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44132</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44134</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44134</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44144</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44147</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44147</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>44147</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>44152</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>44152</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>44154</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>44155</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>44161</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>44165</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44165</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>44171</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>44172</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>44173</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>44174</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>44176</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44179</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44180</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44183</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44207</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44207</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44209</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44209</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44224</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>44228</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44237</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44242</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44245</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44245</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44245</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44247</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44249</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44249</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44251</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>44252</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>44258</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>44258</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>44258</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>44258</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44264</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>44274</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>44274</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>44277</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>44293</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>44298</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>44300</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44302</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44302</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>44305</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>44305</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>44306</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>44306</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44307</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>44307</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>44309</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>44312</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44321</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44321</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44326</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44333</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44334</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44340</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>44340</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>44340</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>44340</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44341</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44341</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>44343</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>44343</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>44343</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>44348</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44349</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>44349</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>44350</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>44351</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>44356</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>44356</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44357</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44357</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>44357</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>44357</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44363</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>44365</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44367</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>44368</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>44368</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44368</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44369</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>44369</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>44370</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>44371</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>44375</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>44377</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>44377</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44379</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>44382</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44383</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44385</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44385</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>44393</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>44403</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>44412</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27161,7 +27161,7 @@
         <v>44412</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>44412</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>44417</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>44417</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>44417</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>44419</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>44421</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>44428</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44428</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44432</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44433</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44437</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44440</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44441</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>44441</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44441</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44442</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44446</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>44453</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>44453</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44460</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44466</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>44469</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44472</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44475</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44476</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44476</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44476</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44476</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44477</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44480</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44487</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44487</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44487</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44488</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44488</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44488</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44488</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44494</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44495</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44496</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44497</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44497</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44501</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44501</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44504</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44505</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44508</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44508</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44508</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44512</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44513</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44516</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44516</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44518</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44524</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44525</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44525</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44526</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44540</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44544</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44544</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44550</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44552</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44552</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44552</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44558</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44564</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44566</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44571</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44571</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>44572</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>44572</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>44572</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>44572</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>44573</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>44573</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44573</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44573</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>44578</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44578</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44581</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44585</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44585</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44592</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44593</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44594</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44595</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>44596</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>44596</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>44599</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>44599</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>44601</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>44603</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>44608</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>44613</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>44613</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>44613</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>44615</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>44615</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>44616</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33067,7 +33067,7 @@
         <v>44617</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44620</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44621</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44627</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44628</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44629</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44630</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44631</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44634</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44634</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44634</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44637</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44641</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44642</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>44648</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44648</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44648</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44648</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>44649</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>44649</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44649</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44655</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44672</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>44676</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44683</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44685</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44687</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44691</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44692</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>44692</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44692</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44692</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44692</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44698</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>44698</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>44702</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44704</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44704</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>44706</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44706</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44713</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44714</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44714</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44725</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44728</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44742</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44743</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>44749</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44750</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44750</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44750</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44750</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44755</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>44768</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44769</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44776</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44776</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>44776</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44776</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44781</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44788</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>44790</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>44790</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44798</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>44802</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>44806</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44806</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44806</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44810</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44812</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44821</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44826</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44827</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44827</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44827</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44830</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44830</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44831</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44831</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44831</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44832</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44834</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>44834</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>44835</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44838</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>44840</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>44844</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>44851</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>44851</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>44852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>44855</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44858</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44861</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44861</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>44861</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>44866</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>44866</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>44866</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44867</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>44868</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44869</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44874</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44874</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44875</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44876</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44876</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44876</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>44887</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44887</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44888</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>44889</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>44889</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>44889</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>44893</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44894</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44895</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44903</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44904</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>44907</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>44907</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44911</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44911</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44911</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44914</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44916</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>44917</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>44918</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>44928</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>44929</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44929</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44930</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44935</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44935</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44935</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44943</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44943</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44943</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44943</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44944</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44944</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44946</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44951</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44951</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>44951</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44951</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>44953</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>44956</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>44956</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44958</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>44958</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44958</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>44958</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>44965</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>44966</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>44966</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>44966</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>44971</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>44977</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>44978</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>44979</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>44980</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>44981</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>44984</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>44988</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>44993</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44997</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44997</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>44998</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45006</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45007</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45008</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45014</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45015</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45021</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45021</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45021</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45022</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45029</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45030</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45034</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45035</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45040</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45040</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45042</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>45043</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45047</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45049</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45049</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45049</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45050</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45050</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45496,7 +45496,7 @@
         <v>45054</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45553,7 +45553,7 @@
         <v>45054</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>45055</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45060</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45062</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45071</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45071</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45072</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45075</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45075</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45076</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45079</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45079</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45082</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45089</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45090</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45090</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45090</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45091</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>45091</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45091</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45092</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45096</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47092,7 +47092,7 @@
         <v>45097</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47149,7 +47149,7 @@
         <v>45097</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45098</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>45098</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45098</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>45103</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>45104</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45107</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45113</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45114</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>45121</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45124</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>45132</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>45139</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45140</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>45140</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48294,7 +48294,7 @@
         <v>45151</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48351,7 +48351,7 @@
         <v>45151</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>45151</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48465,7 +48465,7 @@
         <v>45151</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>45154</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>45155</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45155</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45162</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45162</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>45167</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45167</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>45167</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45168</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45176</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45176</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45180</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>45180</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>45180</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45181</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>45181</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45182</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45189</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>45195</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49890,7 +49890,7 @@
         <v>45195</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>45196</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>45197</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>45198</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50118,7 +50118,7 @@
         <v>45198</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50175,7 +50175,7 @@
         <v>45198</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50232,7 +50232,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>45201</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50346,7 +50346,7 @@
         <v>45202</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>45202</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45203</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45208</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>45209</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50636,7 +50636,7 @@
         <v>45210</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>45210</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>45210</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45212</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45215</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45217</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45218</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>45218</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51325,7 +51325,7 @@
         <v>45224</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>45226</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>45230</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51496,7 +51496,7 @@
         <v>45230</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>45230</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>45230</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>45232</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>45232</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>45233</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>45233</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45233</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>45239</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>45239</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52059,14 +52059,14 @@
     <row r="880" ht="15" customHeight="1">
       <c r="A880" t="inlineStr">
         <is>
-          <t>A 56385-2023</t>
+          <t>A 56381-2023</t>
         </is>
       </c>
       <c r="B880" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52079,7 +52079,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>6.3</v>
+        <v>0.4</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -52116,14 +52116,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 56396-2023</t>
+          <t>A 56523-2023</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52136,7 +52136,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>9</v>
+        <v>1.9</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -52173,14 +52173,14 @@
     <row r="882" ht="15" customHeight="1">
       <c r="A882" t="inlineStr">
         <is>
-          <t>A 56580-2023</t>
+          <t>A 56527-2023</t>
         </is>
       </c>
       <c r="B882" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -52230,14 +52230,14 @@
     <row r="883" ht="15" customHeight="1">
       <c r="A883" t="inlineStr">
         <is>
-          <t>A 56381-2023</t>
+          <t>A 56629-2023</t>
         </is>
       </c>
       <c r="B883" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52250,7 +52250,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>0.4</v>
+        <v>9.6</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -52287,14 +52287,14 @@
     <row r="884" ht="15" customHeight="1">
       <c r="A884" t="inlineStr">
         <is>
-          <t>A 56523-2023</t>
+          <t>A 56580-2023</t>
         </is>
       </c>
       <c r="B884" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52307,7 +52307,7 @@
         </is>
       </c>
       <c r="G884" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -52344,14 +52344,14 @@
     <row r="885" ht="15" customHeight="1">
       <c r="A885" t="inlineStr">
         <is>
-          <t>A 56527-2023</t>
+          <t>A 56385-2023</t>
         </is>
       </c>
       <c r="B885" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         </is>
       </c>
       <c r="G885" t="n">
-        <v>3.8</v>
+        <v>6.3</v>
       </c>
       <c r="H885" t="n">
         <v>0</v>
@@ -52401,14 +52401,14 @@
     <row r="886" ht="15" customHeight="1">
       <c r="A886" t="inlineStr">
         <is>
-          <t>A 56629-2023</t>
+          <t>A 56396-2023</t>
         </is>
       </c>
       <c r="B886" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         </is>
       </c>
       <c r="G886" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="H886" t="n">
         <v>0</v>
@@ -52465,7 +52465,7 @@
         <v>45244</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45244</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45250</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>45250</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>45251</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45253</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45257</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45257</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45258</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45258</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45258</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53095,14 +53095,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 60679-2023</t>
+          <t>A 60739-2023</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -53152,14 +53152,14 @@
     <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 60739-2023</t>
+          <t>A 60679-2023</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53172,7 +53172,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -53216,7 +53216,7 @@
         <v>45261</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45264</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y901"/>
+  <dimension ref="A1:Y903"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>45138</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43644</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>44455</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>44615</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45092</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44505</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>43508</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>43628</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>43970</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44186</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>44613</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>44750</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44866</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44916</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44997</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45184</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45212</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>43573</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>43766</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>44071</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44249</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44417</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>44446</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>44446</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44508</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>44740</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44750</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44750</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>44881</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44889</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45062</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45197</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45229</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45236</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>43314</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43321</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>43336</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>43339</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>43339</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>43339</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>43339</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>43340</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>43348</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>43353</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43353</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43353</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43357</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43357</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43364</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43364</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43376</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>43377</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>43381</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>43383</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>43409</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>43418</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>43420</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>43425</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>43425</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>43427</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>43427</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>43439</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>43446</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>43446</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>43448</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>43452</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>43453</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>43453</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>43453</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>43455</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>43467</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>43468</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>43470</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>43472</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>43474</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>43475</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43475</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43479</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>43479</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>43479</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>43481</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>43482</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>43482</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>43482</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>43486</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>43494</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43495</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>43496</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>43497</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>43497</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43517</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43523</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43534</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>43536</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>43537</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>43538</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>43539</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>43542</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>43544</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>43544</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>43544</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>43544</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>43544</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>43544</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>43550</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>43551</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>43552</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>43556</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>43558</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43560</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>43565</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>43565</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>43565</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>43567</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>43578</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>43579</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>43579</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>43587</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43592</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43593</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43599</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43601</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>43613</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>43613</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>43614</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>43618</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>43618</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>43619</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>43627</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>43633</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43633</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>43635</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>43646</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>43647</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>43648</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>43655</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>43658</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>43670</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>43676</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>43683</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>43690</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>43691</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>43693</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>43693</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>43694</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>43694</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>43696</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>43697</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>43698</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>43698</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>43698</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>43698</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>43700</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>43699</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>43705</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>43707</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>43707</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>43707</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>43709</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>43710</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>43711</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>43712</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>43724</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>43725</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>43731</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>43735</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>43738</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43739</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>43742</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43766</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>43766</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>43766</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>43767</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>43769</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>43769</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>43770</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43774</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43775</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>43777</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>43783</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>43783</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>43784</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43794</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43797</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43797</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>43797</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>43801</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>43803</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>43803</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>43803</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>43805</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>43809</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>43809</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>43811</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>43812</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>43815</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>43815</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>43815</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>43817</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>43817</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>43818</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>43819</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>43837</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>43838</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>43839</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>43846</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>43847</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>43850</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>43854</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>43854</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>43858</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>43859</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>43864</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>43864</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>43864</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43864</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43865</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>43868</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>43868</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>43872</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>43873</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>43873</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43874</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43874</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43880</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>43882</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>43885</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>43892</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>43892</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>43892</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>43899</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>43899</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>43899</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>43899</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>43900</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>43900</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>43900</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>43901</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>43902</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>43903</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>43907</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>43908</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>43909</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>43910</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>43913</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>43913</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>43913</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>43914</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>43915</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>43921</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>43921</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>43924</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>43927</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>43928</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>43930</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>43936</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>43938</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>43938</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>43941</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>43944</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>43944</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>43949</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>43949</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>43949</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>43959</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>43970</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>43999</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>43999</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>43999</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44004</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>44004</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44006</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44007</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>44007</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>44012</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>44015</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>44018</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44031</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>44034</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>44040</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>44041</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>44053</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>44053</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44054</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44055</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>44055</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>44056</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>44062</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44069</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44071</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>44074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>44076</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>44076</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>44076</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>44077</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44084</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>44092</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>44096</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>44099</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44099</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>44105</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44112</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44112</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>44119</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44132</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44132</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44134</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44134</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44144</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44147</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44147</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>44147</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>44152</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>44152</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>44154</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>44155</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>44161</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>44165</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44165</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>44171</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>44172</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>44173</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>44174</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>44176</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44179</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44180</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44183</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44207</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44207</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44209</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44209</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44224</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>44228</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44237</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44242</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44245</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44245</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44245</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44247</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44249</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44249</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44251</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>44252</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>44258</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>44258</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>44258</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>44258</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44264</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>44274</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>44274</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>44277</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>44293</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>44298</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>44300</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44302</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44302</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>44305</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>44305</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>44306</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>44306</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44307</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>44307</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>44309</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>44312</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44321</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44321</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44326</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44333</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44334</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44340</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>44340</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>44340</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>44340</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44341</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44341</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>44343</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>44343</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>44343</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>44348</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44349</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>44349</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>44350</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>44351</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>44356</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>44356</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44357</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44357</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>44357</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>44357</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44363</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>44365</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44367</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>44368</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>44368</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44368</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44369</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>44369</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>44370</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>44371</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>44375</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>44377</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>44377</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44379</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>44382</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44383</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44385</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44385</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>44393</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>44403</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>44412</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27161,7 +27161,7 @@
         <v>44412</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>44412</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>44417</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>44417</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>44417</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>44419</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>44421</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>44428</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44428</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44432</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44433</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44437</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44440</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44441</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>44441</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44441</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44442</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44446</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>44453</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>44453</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44460</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44466</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>44469</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44472</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44475</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44476</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44476</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44476</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44476</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44477</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44480</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44487</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44487</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44487</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44488</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44488</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44488</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44488</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44494</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44495</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44496</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44497</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44497</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44501</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44501</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44504</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44505</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44508</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44508</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44508</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44512</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44513</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44516</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44516</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44518</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44524</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44525</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44525</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44526</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44540</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44544</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44544</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44550</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44552</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44552</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44552</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44558</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44564</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44566</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44571</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44571</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>44572</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>44572</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>44572</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>44572</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>44573</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>44573</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44573</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44573</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>44578</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44578</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44581</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44585</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44585</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44592</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44593</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44594</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44595</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>44596</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>44596</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>44599</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>44599</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>44601</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>44603</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>44608</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>44613</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>44613</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>44613</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>44615</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>44615</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>44616</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33067,7 +33067,7 @@
         <v>44617</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44620</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44621</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44627</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44628</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44629</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44630</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44631</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44634</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44634</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44634</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44637</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44641</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44642</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>44648</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44648</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44648</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44648</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>44649</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>44649</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44649</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44655</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44672</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>44676</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44683</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44685</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44687</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44691</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44692</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>44692</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44692</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44692</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44692</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44698</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>44698</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>44702</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44704</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44704</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>44706</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44706</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44713</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44714</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44714</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44725</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44728</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44742</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44743</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>44749</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44750</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44750</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44750</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44750</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44755</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>44768</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44769</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44776</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44776</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>44776</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44776</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44781</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44788</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>44790</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>44790</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44798</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>44802</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>44806</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44806</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44806</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44810</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44812</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44821</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44826</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44827</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44827</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44827</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44830</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44830</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44831</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44831</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44831</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44832</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44834</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>44834</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>44835</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44838</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>44840</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>44844</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>44851</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>44851</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>44852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>44855</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44858</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44861</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44861</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>44861</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>44866</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>44866</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>44866</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44867</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>44868</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44869</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44874</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44874</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44875</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44876</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44876</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44876</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>44887</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44887</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44888</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>44889</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>44889</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>44889</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>44893</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44894</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44895</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44903</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44904</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>44907</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>44907</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44911</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44911</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44911</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44914</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44916</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>44917</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>44918</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>44928</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>44929</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44929</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44930</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44935</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44935</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44935</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44943</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44943</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44943</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44943</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44944</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44944</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44946</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44951</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44951</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>44951</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44951</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>44953</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>44956</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>44956</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44958</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>44958</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44958</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>44958</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>44965</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>44966</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>44966</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>44966</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>44971</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>44977</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>44978</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>44979</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>44980</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>44981</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>44984</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>44988</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>44993</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44997</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44997</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>44998</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45006</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45007</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45008</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45014</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45015</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45021</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45021</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45021</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45022</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45029</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45030</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45034</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45035</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45040</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45040</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45042</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>45043</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45047</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45049</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45049</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45049</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45050</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45050</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45496,7 +45496,7 @@
         <v>45054</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45553,7 +45553,7 @@
         <v>45054</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>45055</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45060</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45062</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45071</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45071</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45072</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45075</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45075</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45076</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45079</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45079</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45082</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45089</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45090</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45090</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45090</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45091</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>45091</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45091</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45092</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45096</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47092,7 +47092,7 @@
         <v>45097</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47149,7 +47149,7 @@
         <v>45097</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45098</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>45098</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45098</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>45103</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>45104</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45107</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45113</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45114</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>45121</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45124</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>45132</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>45139</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45140</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>45140</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48294,7 +48294,7 @@
         <v>45151</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48351,7 +48351,7 @@
         <v>45151</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>45151</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48465,7 +48465,7 @@
         <v>45151</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>45154</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>45155</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45155</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45162</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45162</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>45167</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45167</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>45167</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45168</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45176</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45176</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45180</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>45180</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>45180</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45181</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>45181</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45182</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45189</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>45195</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49890,7 +49890,7 @@
         <v>45195</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>45196</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>45197</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>45198</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50118,7 +50118,7 @@
         <v>45198</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50175,7 +50175,7 @@
         <v>45198</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50232,7 +50232,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>45201</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50346,7 +50346,7 @@
         <v>45202</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>45202</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45203</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45208</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>45209</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50636,7 +50636,7 @@
         <v>45210</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>45210</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>45210</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45212</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45215</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45217</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45218</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>45218</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51325,7 +51325,7 @@
         <v>45224</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>45226</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>45230</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51496,7 +51496,7 @@
         <v>45230</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>45230</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>45230</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>45232</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>45232</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>45233</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>45233</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45233</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>45239</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>45239</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52059,14 +52059,14 @@
     <row r="880" ht="15" customHeight="1">
       <c r="A880" t="inlineStr">
         <is>
-          <t>A 56381-2023</t>
+          <t>A 56580-2023</t>
         </is>
       </c>
       <c r="B880" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52079,7 +52079,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -52116,14 +52116,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 56523-2023</t>
+          <t>A 56629-2023</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52136,7 +52136,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>1.9</v>
+        <v>9.6</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -52173,14 +52173,14 @@
     <row r="882" ht="15" customHeight="1">
       <c r="A882" t="inlineStr">
         <is>
-          <t>A 56527-2023</t>
+          <t>A 56381-2023</t>
         </is>
       </c>
       <c r="B882" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -52230,14 +52230,14 @@
     <row r="883" ht="15" customHeight="1">
       <c r="A883" t="inlineStr">
         <is>
-          <t>A 56629-2023</t>
+          <t>A 56385-2023</t>
         </is>
       </c>
       <c r="B883" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52250,7 +52250,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>9.6</v>
+        <v>6.3</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -52287,14 +52287,14 @@
     <row r="884" ht="15" customHeight="1">
       <c r="A884" t="inlineStr">
         <is>
-          <t>A 56580-2023</t>
+          <t>A 56396-2023</t>
         </is>
       </c>
       <c r="B884" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52307,7 +52307,7 @@
         </is>
       </c>
       <c r="G884" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -52344,14 +52344,14 @@
     <row r="885" ht="15" customHeight="1">
       <c r="A885" t="inlineStr">
         <is>
-          <t>A 56385-2023</t>
+          <t>A 56527-2023</t>
         </is>
       </c>
       <c r="B885" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         </is>
       </c>
       <c r="G885" t="n">
-        <v>6.3</v>
+        <v>3.8</v>
       </c>
       <c r="H885" t="n">
         <v>0</v>
@@ -52401,14 +52401,14 @@
     <row r="886" ht="15" customHeight="1">
       <c r="A886" t="inlineStr">
         <is>
-          <t>A 56396-2023</t>
+          <t>A 56523-2023</t>
         </is>
       </c>
       <c r="B886" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         </is>
       </c>
       <c r="G886" t="n">
-        <v>9</v>
+        <v>1.9</v>
       </c>
       <c r="H886" t="n">
         <v>0</v>
@@ -52465,7 +52465,7 @@
         <v>45244</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45244</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52572,14 +52572,14 @@
     <row r="889" ht="15" customHeight="1">
       <c r="A889" t="inlineStr">
         <is>
-          <t>A 58381-2023</t>
+          <t>A 59032-2023</t>
         </is>
       </c>
       <c r="B889" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52591,8 +52591,13 @@
           <t>BENGTSFORS</t>
         </is>
       </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G889" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="H889" t="n">
         <v>0</v>
@@ -52629,14 +52634,14 @@
     <row r="890" ht="15" customHeight="1">
       <c r="A890" t="inlineStr">
         <is>
-          <t>A 59032-2023</t>
+          <t>A 58381-2023</t>
         </is>
       </c>
       <c r="B890" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52648,13 +52653,8 @@
           <t>BENGTSFORS</t>
         </is>
       </c>
-      <c r="F890" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G890" t="n">
-        <v>6.6</v>
+        <v>3.3</v>
       </c>
       <c r="H890" t="n">
         <v>0</v>
@@ -52698,7 +52698,7 @@
         <v>45251</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45253</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52810,14 +52810,14 @@
     <row r="893" ht="15" customHeight="1">
       <c r="A893" t="inlineStr">
         <is>
-          <t>A 59980-2023</t>
+          <t>A 59979-2023</t>
         </is>
       </c>
       <c r="B893" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52867,14 +52867,14 @@
     <row r="894" ht="15" customHeight="1">
       <c r="A894" t="inlineStr">
         <is>
-          <t>A 59979-2023</t>
+          <t>A 59980-2023</t>
         </is>
       </c>
       <c r="B894" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45258</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52981,14 +52981,14 @@
     <row r="896" ht="15" customHeight="1">
       <c r="A896" t="inlineStr">
         <is>
-          <t>A 60177-2023</t>
+          <t>A 60066-2023</t>
         </is>
       </c>
       <c r="B896" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         </is>
       </c>
       <c r="G896" t="n">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
       <c r="H896" t="n">
         <v>0</v>
@@ -53038,14 +53038,14 @@
     <row r="897" ht="15" customHeight="1">
       <c r="A897" t="inlineStr">
         <is>
-          <t>A 60066-2023</t>
+          <t>A 60177-2023</t>
         </is>
       </c>
       <c r="B897" s="1" t="n">
         <v>45258</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53058,7 +53058,7 @@
         </is>
       </c>
       <c r="G897" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="H897" t="n">
         <v>0</v>
@@ -53102,7 +53102,7 @@
         <v>45260</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45260</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45261</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53263,7 +53263,7 @@
       </c>
       <c r="R900" s="2" t="inlineStr"/>
     </row>
-    <row r="901">
+    <row r="901" ht="15" customHeight="1">
       <c r="A901" t="inlineStr">
         <is>
           <t>A 61334-2023</t>
@@ -53273,7 +53273,7 @@
         <v>45264</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45267</v>
+        <v>45268</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53319,6 +53319,120 @@
         <v>0</v>
       </c>
       <c r="R901" s="2" t="inlineStr"/>
+    </row>
+    <row r="902" ht="15" customHeight="1">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>A 62192-2023</t>
+        </is>
+      </c>
+      <c r="B902" s="1" t="n">
+        <v>45267</v>
+      </c>
+      <c r="C902" s="1" t="n">
+        <v>45268</v>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>BENGTSFORS</t>
+        </is>
+      </c>
+      <c r="G902" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H902" t="n">
+        <v>0</v>
+      </c>
+      <c r="I902" t="n">
+        <v>0</v>
+      </c>
+      <c r="J902" t="n">
+        <v>0</v>
+      </c>
+      <c r="K902" t="n">
+        <v>0</v>
+      </c>
+      <c r="L902" t="n">
+        <v>0</v>
+      </c>
+      <c r="M902" t="n">
+        <v>0</v>
+      </c>
+      <c r="N902" t="n">
+        <v>0</v>
+      </c>
+      <c r="O902" t="n">
+        <v>0</v>
+      </c>
+      <c r="P902" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q902" t="n">
+        <v>0</v>
+      </c>
+      <c r="R902" s="2" t="inlineStr"/>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>A 62190-2023</t>
+        </is>
+      </c>
+      <c r="B903" s="1" t="n">
+        <v>45267</v>
+      </c>
+      <c r="C903" s="1" t="n">
+        <v>45268</v>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>BENGTSFORS</t>
+        </is>
+      </c>
+      <c r="G903" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H903" t="n">
+        <v>0</v>
+      </c>
+      <c r="I903" t="n">
+        <v>0</v>
+      </c>
+      <c r="J903" t="n">
+        <v>0</v>
+      </c>
+      <c r="K903" t="n">
+        <v>0</v>
+      </c>
+      <c r="L903" t="n">
+        <v>0</v>
+      </c>
+      <c r="M903" t="n">
+        <v>0</v>
+      </c>
+      <c r="N903" t="n">
+        <v>0</v>
+      </c>
+      <c r="O903" t="n">
+        <v>0</v>
+      </c>
+      <c r="P903" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q903" t="n">
+        <v>0</v>
+      </c>
+      <c r="R903" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y903"/>
+  <dimension ref="A1:Y904"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>45138</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43644</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>44455</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>44615</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45092</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44505</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>43508</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>43628</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>43970</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44186</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>44613</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>44750</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44866</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44916</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44997</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45184</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45212</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>43573</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>43766</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>44071</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44249</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44417</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>44446</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>44446</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44508</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>44740</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44750</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44750</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>44881</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44889</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45062</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45197</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45229</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45236</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>43314</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43321</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>43336</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>43339</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>43339</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>43339</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>43339</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>43340</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>43348</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>43353</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43353</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43353</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43357</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43357</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43364</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43364</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43376</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>43377</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>43381</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>43383</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>43409</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>43418</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>43420</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>43425</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>43425</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>43427</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>43427</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>43439</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>43446</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>43446</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>43448</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>43452</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>43453</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>43453</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>43453</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>43455</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>43467</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>43468</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>43470</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>43472</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>43474</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>43475</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43475</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43479</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>43479</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>43479</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>43481</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>43482</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>43482</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>43482</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>43486</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>43494</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43495</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>43496</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>43497</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>43497</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43517</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43523</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43534</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>43536</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>43537</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>43538</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>43539</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>43542</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>43544</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>43544</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>43544</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>43544</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>43544</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>43544</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>43550</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>43551</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>43552</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>43556</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>43558</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>43560</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>43565</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>43565</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>43565</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>43567</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>43567</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>43578</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>43579</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>43579</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>43587</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>43592</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>43593</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>43599</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>43601</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>43613</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>43613</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>43614</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>43618</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>43618</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>43619</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>43627</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>43633</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>43633</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>43635</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>43635</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>43646</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>43647</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>43648</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>43655</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>43658</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>43670</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>43676</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>43683</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>43690</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>43691</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>43693</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>43693</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>43694</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>43694</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>43696</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>43697</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>43697</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>43698</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>43698</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>43698</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>43698</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>43700</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>43699</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>43705</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>43707</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>43707</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>43707</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         <v>43709</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>43710</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>43711</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>43712</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>43712</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>43713</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>43717</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>43724</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>43725</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>43731</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>43735</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>43738</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>43739</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>43742</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>43766</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>43766</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>43766</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>43767</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>43769</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>43769</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>43770</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>43774</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>43774</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>43775</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>43776</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>43777</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>43781</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>43783</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>43783</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>43784</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>43787</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>43794</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>43796</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>43797</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>43797</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>43797</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>43797</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>43797</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>43801</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>43803</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>43803</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>43803</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>43805</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>43809</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>43809</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>43811</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>43812</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>43815</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>43815</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>43815</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>43817</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>43817</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>43818</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>43819</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>43837</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>43838</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>43839</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>43846</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>43847</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>43850</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>43854</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>43854</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>43858</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>43859</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>43864</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>43864</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>43864</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>43864</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>43865</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>43868</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>43868</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>43872</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>43873</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>43873</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>43874</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>43874</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>43880</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>43882</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>43885</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>43892</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>43892</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>43892</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>43894</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>43894</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>43899</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>43899</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>43899</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>43899</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>43900</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>43900</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>43900</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>43901</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>43902</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>43903</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>43907</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>43908</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>43909</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>43910</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>43913</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>43913</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>43913</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>43914</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>43915</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>43921</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>43921</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>43924</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>43927</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>43928</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>43930</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>43936</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>43938</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>43938</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>43941</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>43944</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>43944</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>43949</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>43949</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>43949</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>43959</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>43970</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>43999</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>43999</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>43999</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>44004</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>44004</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18806,7 +18806,7 @@
         <v>44006</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44007</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>44007</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>44012</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>44015</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>44018</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>44031</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>44034</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>44040</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>44041</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>44053</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>44053</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44054</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>44055</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>44055</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>44056</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>44062</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44069</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44071</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>44074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>44076</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>44076</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>44076</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>44077</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44084</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>44092</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>44096</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>44099</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44099</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>44105</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44112</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>44112</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>44119</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44132</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44132</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>44134</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20893,7 +20893,7 @@
         <v>44134</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>44144</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44147</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44147</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>44147</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>44152</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>44152</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>44154</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>44155</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>44161</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>44165</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44165</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>44167</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>44171</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>44172</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>44173</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>44174</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>44176</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44179</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44180</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
         <v>44183</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>44207</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>44207</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>44209</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>44209</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>44215</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44224</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>44228</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>44237</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44242</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>44245</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>44245</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44245</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>44247</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44249</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>44249</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44251</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>44252</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>44258</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>44258</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>44258</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>44258</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44264</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>44274</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>44274</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>44277</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>44293</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>44298</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>44300</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>44300</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>44300</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44302</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44302</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>44305</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>44305</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>44306</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>44306</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44307</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>44307</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>44309</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>44312</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44321</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44321</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44326</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44333</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44334</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44340</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>44340</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>44340</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>44340</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44341</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44341</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>44343</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>44343</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>44343</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>44348</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44349</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>44349</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>44350</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25545,7 +25545,7 @@
         <v>44351</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>44356</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>44356</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>44357</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>44357</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>44357</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>44357</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44363</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>44365</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44367</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>44368</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>44368</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44368</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>44369</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26348,7 +26348,7 @@
         <v>44369</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26405,7 +26405,7 @@
         <v>44370</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>44371</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>44375</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>44377</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>44377</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44379</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>44382</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>44383</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44385</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44385</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>44393</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27047,7 +27047,7 @@
         <v>44403</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>44412</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27161,7 +27161,7 @@
         <v>44412</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>44412</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>44417</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>44417</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>44417</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>44419</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>44421</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>44428</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>44428</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>44432</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>44433</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>44437</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>44440</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44441</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>44441</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44441</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44442</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44446</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>44453</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>44453</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44460</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>44466</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>44469</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44472</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44475</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44476</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44476</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44476</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44476</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>44477</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>44480</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>44487</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>44487</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>44487</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>44488</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44488</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>44488</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>44488</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44494</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>44495</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>44496</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>44497</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>44497</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>44501</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>44501</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>44504</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29927,7 +29927,7 @@
         <v>44505</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>44508</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>44508</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44508</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>44512</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>44513</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>44516</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>44516</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>44518</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44524</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>44525</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44525</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>44526</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>44540</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44544</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44544</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44550</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44552</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>44552</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>44552</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44558</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44564</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>44566</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>44571</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>44571</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>44572</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>44572</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>44572</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>44572</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>44573</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>44573</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44573</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44573</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>44578</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31865,7 +31865,7 @@
         <v>44578</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31922,7 +31922,7 @@
         <v>44581</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>44585</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>44585</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44592</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44593</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>44594</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>44595</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>44596</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>44596</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>44599</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>44599</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>44601</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>44603</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32668,7 +32668,7 @@
         <v>44608</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>44613</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>44613</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         <v>44613</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>44615</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>44615</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>44616</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33067,7 +33067,7 @@
         <v>44617</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44620</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>44621</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>44627</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>44628</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33357,7 +33357,7 @@
         <v>44629</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44630</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>44631</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>44634</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>44634</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>44634</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>44637</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44641</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44642</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>44648</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>44648</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>44648</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>44648</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>44649</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34155,7 +34155,7 @@
         <v>44649</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>44649</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>44655</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44672</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>44676</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>44683</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34497,7 +34497,7 @@
         <v>44685</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>44687</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>44691</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>44692</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>44692</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>44692</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>44692</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>44692</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>44694</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35010,7 +35010,7 @@
         <v>44698</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>44698</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>44702</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>44704</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44704</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>44706</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>44706</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44713</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44714</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35523,7 +35523,7 @@
         <v>44714</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44725</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>44728</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44742</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>44743</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35808,7 +35808,7 @@
         <v>44749</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44750</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>44750</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44750</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44750</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>44755</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>44768</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36207,7 +36207,7 @@
         <v>44769</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36264,7 +36264,7 @@
         <v>44776</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36321,7 +36321,7 @@
         <v>44776</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36378,7 +36378,7 @@
         <v>44776</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>44776</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>44781</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>44788</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>44790</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>44790</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>44798</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>44802</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>44806</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44806</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44806</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44810</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44812</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>44821</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>44826</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44827</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44827</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>44827</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>44830</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>44830</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>44831</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>44831</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>44831</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44832</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>44834</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>44834</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37875,7 +37875,7 @@
         <v>44834</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>44835</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44838</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44839</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>44839</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>44840</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>44844</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>44845</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38336,7 +38336,7 @@
         <v>44845</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38393,7 +38393,7 @@
         <v>44851</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38450,7 +38450,7 @@
         <v>44851</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38507,7 +38507,7 @@
         <v>44852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>44853</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>44855</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44858</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>44861</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44861</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>44861</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>44866</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>44866</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>44866</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44867</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>44868</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>44868</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>44869</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44874</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>44874</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>44875</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>44876</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>44876</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>44876</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>44887</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44887</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44888</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>44889</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>44889</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>44889</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>44893</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44894</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44895</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>44901</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44903</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>44904</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>44907</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>44907</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44911</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44911</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44911</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44914</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44916</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>44917</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>44918</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>44928</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>44929</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44929</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         <v>44930</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>44935</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44935</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44935</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44943</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44943</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44943</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44943</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44944</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44944</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44946</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44951</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44951</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>44951</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>44951</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>44953</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>44956</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>44956</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>44956</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>44958</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>44958</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44958</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>44958</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>44964</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>44964</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>44965</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>44966</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>44966</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>44966</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44967</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>44971</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>44977</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>44978</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>44979</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>44980</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>44981</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>44984</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>44988</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>44993</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44997</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44997</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>44998</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>45002</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45006</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>45007</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45007</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45007</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45007</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45007</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45008</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45008</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45014</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45015</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45021</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45021</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45021</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45022</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45029</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45030</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45034</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45035</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>45040</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45040</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45040,7 +45040,7 @@
         <v>45042</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>45043</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>45047</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>45049</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45268,7 +45268,7 @@
         <v>45049</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45049</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45050</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45050</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45496,7 +45496,7 @@
         <v>45054</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45553,7 +45553,7 @@
         <v>45054</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45610,7 +45610,7 @@
         <v>45055</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45060</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>45062</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45062</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45063</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45068</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45071</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45071</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>45071</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45072</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45075</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45075</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45076</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45079</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46408,7 +46408,7 @@
         <v>45079</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>45082</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>45084</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>45089</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         <v>45090</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45090</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>45090</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45091</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>45091</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>45091</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45092</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>45096</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47092,7 +47092,7 @@
         <v>45097</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47149,7 +47149,7 @@
         <v>45097</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47206,7 +47206,7 @@
         <v>45098</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47263,7 +47263,7 @@
         <v>45098</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47320,7 +47320,7 @@
         <v>45098</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47377,7 +47377,7 @@
         <v>45103</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>45104</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47491,7 +47491,7 @@
         <v>45107</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47548,7 +47548,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45110</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>45111</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45111</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45112</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45113</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45114</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>45121</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45124</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>45132</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>45139</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48180,7 +48180,7 @@
         <v>45140</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>45140</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48294,7 +48294,7 @@
         <v>45151</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48351,7 +48351,7 @@
         <v>45151</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>45151</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48465,7 +48465,7 @@
         <v>45151</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>45154</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>45155</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45155</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45155</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45156</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45162</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45162</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>45167</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45167</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>45167</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45168</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45168</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45173</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45176</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45176</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45180</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>45180</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>45180</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45181</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>45181</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45182</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45189</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45189</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>45195</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49890,7 +49890,7 @@
         <v>45195</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>45196</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>45197</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>45198</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50118,7 +50118,7 @@
         <v>45198</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50175,7 +50175,7 @@
         <v>45198</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50232,7 +50232,7 @@
         <v>45201</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>45201</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50346,7 +50346,7 @@
         <v>45202</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50403,7 +50403,7 @@
         <v>45202</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50460,7 +50460,7 @@
         <v>45203</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45208</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50579,7 +50579,7 @@
         <v>45209</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50636,7 +50636,7 @@
         <v>45210</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>45210</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>45210</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45212</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45215</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45217</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45217</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>45218</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51097,7 +51097,7 @@
         <v>45218</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>45218</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>45223</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51325,7 +51325,7 @@
         <v>45224</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>45226</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>45230</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51496,7 +51496,7 @@
         <v>45230</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>45230</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>45230</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>45232</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>45232</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>45233</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>45233</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>45233</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51952,7 +51952,7 @@
         <v>45239</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>45239</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52059,14 +52059,14 @@
     <row r="880" ht="15" customHeight="1">
       <c r="A880" t="inlineStr">
         <is>
-          <t>A 56580-2023</t>
+          <t>A 56381-2023</t>
         </is>
       </c>
       <c r="B880" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52079,7 +52079,7 @@
         </is>
       </c>
       <c r="G880" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H880" t="n">
         <v>0</v>
@@ -52116,14 +52116,14 @@
     <row r="881" ht="15" customHeight="1">
       <c r="A881" t="inlineStr">
         <is>
-          <t>A 56629-2023</t>
+          <t>A 56523-2023</t>
         </is>
       </c>
       <c r="B881" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52136,7 +52136,7 @@
         </is>
       </c>
       <c r="G881" t="n">
-        <v>9.6</v>
+        <v>1.9</v>
       </c>
       <c r="H881" t="n">
         <v>0</v>
@@ -52173,14 +52173,14 @@
     <row r="882" ht="15" customHeight="1">
       <c r="A882" t="inlineStr">
         <is>
-          <t>A 56381-2023</t>
+          <t>A 56527-2023</t>
         </is>
       </c>
       <c r="B882" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
         </is>
       </c>
       <c r="G882" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -52230,14 +52230,14 @@
     <row r="883" ht="15" customHeight="1">
       <c r="A883" t="inlineStr">
         <is>
-          <t>A 56385-2023</t>
+          <t>A 56629-2023</t>
         </is>
       </c>
       <c r="B883" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52250,7 +52250,7 @@
         </is>
       </c>
       <c r="G883" t="n">
-        <v>6.3</v>
+        <v>9.6</v>
       </c>
       <c r="H883" t="n">
         <v>0</v>
@@ -52287,14 +52287,14 @@
     <row r="884" ht="15" customHeight="1">
       <c r="A884" t="inlineStr">
         <is>
-          <t>A 56396-2023</t>
+          <t>A 56385-2023</t>
         </is>
       </c>
       <c r="B884" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52307,7 +52307,7 @@
         </is>
       </c>
       <c r="G884" t="n">
-        <v>9</v>
+        <v>6.3</v>
       </c>
       <c r="H884" t="n">
         <v>0</v>
@@ -52344,14 +52344,14 @@
     <row r="885" ht="15" customHeight="1">
       <c r="A885" t="inlineStr">
         <is>
-          <t>A 56527-2023</t>
+          <t>A 56396-2023</t>
         </is>
       </c>
       <c r="B885" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         </is>
       </c>
       <c r="G885" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="H885" t="n">
         <v>0</v>
@@ -52401,14 +52401,14 @@
     <row r="886" ht="15" customHeight="1">
       <c r="A886" t="inlineStr">
         <is>
-          <t>A 56523-2023</t>
+          <t>A 56580-2023</t>
         </is>
       </c>
       <c r="B886" s="1" t="n">
         <v>45243</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         </is>
       </c>
       <c r="G886" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="H886" t="n">
         <v>0</v>
@@ -52465,7 +52465,7 @@
         <v>45244</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45244</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52572,14 +52572,14 @@
     <row r="889" ht="15" customHeight="1">
       <c r="A889" t="inlineStr">
         <is>
-          <t>A 59032-2023</t>
+          <t>A 58381-2023</t>
         </is>
       </c>
       <c r="B889" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52591,13 +52591,8 @@
           <t>BENGTSFORS</t>
         </is>
       </c>
-      <c r="F889" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="G889" t="n">
-        <v>6.6</v>
+        <v>3.3</v>
       </c>
       <c r="H889" t="n">
         <v>0</v>
@@ -52634,14 +52629,14 @@
     <row r="890" ht="15" customHeight="1">
       <c r="A890" t="inlineStr">
         <is>
-          <t>A 58381-2023</t>
+          <t>A 59032-2023</t>
         </is>
       </c>
       <c r="B890" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52653,8 +52648,13 @@
           <t>BENGTSFORS</t>
         </is>
       </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="G890" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="H890" t="n">
         <v>0</v>
@@ -52698,7 +52698,7 @@
         <v>45251</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45253</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45257</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45257</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45258</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45258</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45258</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53095,14 +53095,14 @@
     <row r="898" ht="15" customHeight="1">
       <c r="A898" t="inlineStr">
         <is>
-          <t>A 60739-2023</t>
+          <t>A 60679-2023</t>
         </is>
       </c>
       <c r="B898" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53115,7 +53115,7 @@
         </is>
       </c>
       <c r="G898" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="H898" t="n">
         <v>0</v>
@@ -53152,14 +53152,14 @@
     <row r="899" ht="15" customHeight="1">
       <c r="A899" t="inlineStr">
         <is>
-          <t>A 60679-2023</t>
+          <t>A 60739-2023</t>
         </is>
       </c>
       <c r="B899" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53172,7 +53172,7 @@
         </is>
       </c>
       <c r="G899" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="H899" t="n">
         <v>0</v>
@@ -53216,7 +53216,7 @@
         <v>45261</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45264</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53323,14 +53323,14 @@
     <row r="902" ht="15" customHeight="1">
       <c r="A902" t="inlineStr">
         <is>
-          <t>A 62192-2023</t>
+          <t>A 62190-2023</t>
         </is>
       </c>
       <c r="B902" s="1" t="n">
         <v>45267</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45268</v>
+        <v>45269</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53343,7 +53343,7 @@
         </is>
       </c>
       <c r="G902" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="H902" t="n">
         <v>0</v>
@@ -53377,62 +53377,119 @@
       </c>
       <c r="R902" s="2" t="inlineStr"/>
     </row>
-    <row r="903">
+    <row r="903" ht="15" customHeight="1">
       <c r="A903" t="inlineStr">
         <is>
-          <t>A 62190-2023</t>
+          <t>A 62192-2023</t>
         </is>
       </c>
       <c r="B903" s="1" t="n">
         <v>45267</v>
       </c>
       <c r="C903" s="1" t="n">
+        <v>45269</v>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>BENGTSFORS</t>
+        </is>
+      </c>
+      <c r="G903" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H903" t="n">
+        <v>0</v>
+      </c>
+      <c r="I903" t="n">
+        <v>0</v>
+      </c>
+      <c r="J903" t="n">
+        <v>0</v>
+      </c>
+      <c r="K903" t="n">
+        <v>0</v>
+      </c>
+      <c r="L903" t="n">
+        <v>0</v>
+      </c>
+      <c r="M903" t="n">
+        <v>0</v>
+      </c>
+      <c r="N903" t="n">
+        <v>0</v>
+      </c>
+      <c r="O903" t="n">
+        <v>0</v>
+      </c>
+      <c r="P903" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q903" t="n">
+        <v>0</v>
+      </c>
+      <c r="R903" s="2" t="inlineStr"/>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>A 62503-2023</t>
+        </is>
+      </c>
+      <c r="B904" s="1" t="n">
         <v>45268</v>
       </c>
-      <c r="D903" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="E903" t="inlineStr">
-        <is>
-          <t>BENGTSFORS</t>
-        </is>
-      </c>
-      <c r="G903" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H903" t="n">
-        <v>0</v>
-      </c>
-      <c r="I903" t="n">
-        <v>0</v>
-      </c>
-      <c r="J903" t="n">
-        <v>0</v>
-      </c>
-      <c r="K903" t="n">
-        <v>0</v>
-      </c>
-      <c r="L903" t="n">
-        <v>0</v>
-      </c>
-      <c r="M903" t="n">
-        <v>0</v>
-      </c>
-      <c r="N903" t="n">
-        <v>0</v>
-      </c>
-      <c r="O903" t="n">
-        <v>0</v>
-      </c>
-      <c r="P903" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q903" t="n">
-        <v>0</v>
-      </c>
-      <c r="R903" s="2" t="inlineStr"/>
+      <c r="C904" s="1" t="n">
+        <v>45269</v>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>BENGTSFORS</t>
+        </is>
+      </c>
+      <c r="G904" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H904" t="n">
+        <v>0</v>
+      </c>
+      <c r="I904" t="n">
+        <v>0</v>
+      </c>
+      <c r="J904" t="n">
+        <v>0</v>
+      </c>
+      <c r="K904" t="n">
+        <v>0</v>
+      </c>
+      <c r="L904" t="n">
+        <v>0</v>
+      </c>
+      <c r="M904" t="n">
+        <v>0</v>
+      </c>
+      <c r="N904" t="n">
+        <v>0</v>
+      </c>
+      <c r="O904" t="n">
+        <v>0</v>
+      </c>
+      <c r="P904" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q904" t="n">
+        <v>0</v>
+      </c>
+      <c r="R904" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt BENGTSFORS.xlsx
+++ b/Översikt BENGTSFORS.xlsx
@@ -564,7 +564,7 @@
         <v>45138</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>43644</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>44455</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>44615</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>45092</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44438</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>44505</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>43508</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>43628</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>43970</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>44186</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>44613</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>44750</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44866</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>44916</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>44951</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44997</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45184</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>45212</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>43573</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>43766</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>44071</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44249</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44417</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>44446</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>44446</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44508</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>44740</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44750</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44750</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>44881</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44889</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45062</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45197</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>45229</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45236</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>43314</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>43321</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>43336</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>43339</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>43339</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v>43339</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>43339</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>43340</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>43348</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>43353</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>43353</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>43353</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>43357</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>43357</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>43364</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>43364</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>43376</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>43376</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>43377</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>43381</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>43383</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>43388</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>43390</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>43409</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>43418</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>43419</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>43420</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>43425</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>43425</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>43427</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>43427</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>43439</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>43446</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>43446</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>43448</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>43452</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>43453</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>43453</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>43453</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>43455</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>43467</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>43468</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>43470</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>43472</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>43474</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>43474</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>43474</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>43475</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>43475</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>43479</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>43479</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>43479</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>43481</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>43482</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>43482</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>43482</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>43486</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>43494</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>43495</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>43496</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>43497</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>43497</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>43508</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>43508</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>43517</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>43523</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>43534</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>43536</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>43537</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>43538</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>43539</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>43542</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>43544</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>43544</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>43544</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>43544</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>43544</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>43544</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>43544</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         <v>43550</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>43551</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>